--- a/suivi_reseaux_politiques.xlsx
+++ b/suivi_reseaux_politiques.xlsx
@@ -13,7 +13,7 @@
     <sheet name="_donnees_graphiques" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DONNEES'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DONNEES'!$A$1:$H$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,12 +431,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$B$3:$B$5</f>
+              <f>'_donnees_graphiques'!$B$3:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -467,12 +467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$C$3:$C$5</f>
+              <f>'_donnees_graphiques'!$C$3:$C$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -503,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$D$3:$D$5</f>
+              <f>'_donnees_graphiques'!$D$3:$D$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -539,12 +539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$E$3:$E$5</f>
+              <f>'_donnees_graphiques'!$E$3:$E$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -575,12 +575,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$F$3:$F$5</f>
+              <f>'_donnees_graphiques'!$F$3:$F$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -611,12 +611,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$G$3:$G$5</f>
+              <f>'_donnees_graphiques'!$G$3:$G$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -647,12 +647,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$5</f>
+              <f>'_donnees_graphiques'!$H$3:$H$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -683,12 +683,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$I$3:$I$5</f>
+              <f>'_donnees_graphiques'!$I$3:$I$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -719,12 +719,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$J$3:$J$5</f>
+              <f>'_donnees_graphiques'!$J$3:$J$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -755,12 +755,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$5</f>
+              <f>'_donnees_graphiques'!$A$3:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$K$3:$K$5</f>
+              <f>'_donnees_graphiques'!$K$3:$K$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -878,12 +878,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$N$3:$N$5</f>
+              <f>'_donnees_graphiques'!$N$3:$N$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -914,12 +914,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$O$3:$O$5</f>
+              <f>'_donnees_graphiques'!$O$3:$O$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -950,12 +950,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$P$3:$P$5</f>
+              <f>'_donnees_graphiques'!$P$3:$P$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -986,12 +986,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$Q$3:$Q$5</f>
+              <f>'_donnees_graphiques'!$Q$3:$Q$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$R$3:$R$5</f>
+              <f>'_donnees_graphiques'!$R$3:$R$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1058,12 +1058,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$S$3:$S$5</f>
+              <f>'_donnees_graphiques'!$S$3:$S$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$T$3:$T$5</f>
+              <f>'_donnees_graphiques'!$T$3:$T$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1130,12 +1130,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$U$3:$U$5</f>
+              <f>'_donnees_graphiques'!$U$3:$U$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1166,12 +1166,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$V$3:$V$5</f>
+              <f>'_donnees_graphiques'!$V$3:$V$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1202,12 +1202,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$5</f>
+              <f>'_donnees_graphiques'!$M$3:$M$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$W$3:$W$5</f>
+              <f>'_donnees_graphiques'!$W$3:$W$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1325,12 +1325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$Z$3:$Z$5</f>
+              <f>'_donnees_graphiques'!$Z$3:$Z$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1361,12 +1361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AA$3:$AA$5</f>
+              <f>'_donnees_graphiques'!$AA$3:$AA$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1397,12 +1397,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AB$3:$AB$5</f>
+              <f>'_donnees_graphiques'!$AB$3:$AB$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1433,12 +1433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AC$3:$AC$5</f>
+              <f>'_donnees_graphiques'!$AC$3:$AC$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1469,12 +1469,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AD$3:$AD$5</f>
+              <f>'_donnees_graphiques'!$AD$3:$AD$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1505,12 +1505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AE$3:$AE$5</f>
+              <f>'_donnees_graphiques'!$AE$3:$AE$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1541,12 +1541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AF$3:$AF$5</f>
+              <f>'_donnees_graphiques'!$AF$3:$AF$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1577,12 +1577,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AG$3:$AG$5</f>
+              <f>'_donnees_graphiques'!$AG$3:$AG$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1613,12 +1613,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AH$3:$AH$5</f>
+              <f>'_donnees_graphiques'!$AH$3:$AH$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1649,12 +1649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$5</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AI$3:$AI$5</f>
+              <f>'_donnees_graphiques'!$AI$3:$AI$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1772,12 +1772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AL$3:$AL$5</f>
+              <f>'_donnees_graphiques'!$AL$3:$AL$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1808,12 +1808,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AM$3:$AM$5</f>
+              <f>'_donnees_graphiques'!$AM$3:$AM$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1844,12 +1844,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AN$3:$AN$5</f>
+              <f>'_donnees_graphiques'!$AN$3:$AN$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1880,12 +1880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AO$3:$AO$5</f>
+              <f>'_donnees_graphiques'!$AO$3:$AO$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1916,12 +1916,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AP$3:$AP$5</f>
+              <f>'_donnees_graphiques'!$AP$3:$AP$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1952,12 +1952,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AQ$3:$AQ$5</f>
+              <f>'_donnees_graphiques'!$AQ$3:$AQ$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1988,12 +1988,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AR$3:$AR$5</f>
+              <f>'_donnees_graphiques'!$AR$3:$AR$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AS$3:$AS$5</f>
+              <f>'_donnees_graphiques'!$AS$3:$AS$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AT$3:$AT$5</f>
+              <f>'_donnees_graphiques'!$AT$3:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2096,12 +2096,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$5</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AU$3:$AU$5</f>
+              <f>'_donnees_graphiques'!$AU$3:$AU$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2219,12 +2219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AX$3:$AX$5</f>
+              <f>'_donnees_graphiques'!$AX$3:$AX$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2255,12 +2255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AY$3:$AY$5</f>
+              <f>'_donnees_graphiques'!$AY$3:$AY$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2291,12 +2291,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AZ$3:$AZ$5</f>
+              <f>'_donnees_graphiques'!$AZ$3:$AZ$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2327,12 +2327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BA$3:$BA$5</f>
+              <f>'_donnees_graphiques'!$BA$3:$BA$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2363,12 +2363,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BB$3:$BB$5</f>
+              <f>'_donnees_graphiques'!$BB$3:$BB$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2399,12 +2399,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BC$3:$BC$5</f>
+              <f>'_donnees_graphiques'!$BC$3:$BC$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BD$3:$BD$5</f>
+              <f>'_donnees_graphiques'!$BD$3:$BD$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2471,12 +2471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BE$3:$BE$5</f>
+              <f>'_donnees_graphiques'!$BE$3:$BE$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2507,12 +2507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BF$3:$BF$5</f>
+              <f>'_donnees_graphiques'!$BF$3:$BF$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2543,12 +2543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$5</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BG$3:$BG$5</f>
+              <f>'_donnees_graphiques'!$BG$3:$BG$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3023,7 +3023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3882,8 +3882,288 @@
         <v>577200</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>175101</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>192100</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>101000</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>18500</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>575701</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>105710</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>213300</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n">
+        <v>84900</v>
+      </c>
+      <c r="H33" s="23" t="n">
+        <v>521910</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>218132</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>941200</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>266000</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>431000</v>
+      </c>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n">
+        <v>1856332</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>462184</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>286700</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n">
+        <v>682100</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>1610984</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>30730</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>205400</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="19" t="n">
+        <v>335130</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="n">
+        <v>757103</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>7357103</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>1402566</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>625900</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>5628466</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="n">
+        <v>847736</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>8347736</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>636883</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>307800</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>398000</v>
+      </c>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="19" t="n">
+        <v>1522683</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="n">
+        <v>356879</v>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>136200</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n">
+        <v>85400</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>658479</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H31"/>
+  <autoFilter ref="A1:H41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3895,7 +4175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3921,7 +4201,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Dernier releve : 02/09/2026   -   10 personnalites suivies</t>
+          <t>Dernier releve : 03/09/2026   -   10 personnalites suivies</t>
         </is>
       </c>
     </row>
@@ -4005,14 +4285,14 @@
     <row r="7">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Marine Le Pen</t>
+          <t>Jean-Luc Mélenchon</t>
         </is>
       </c>
       <c r="B7" s="31" t="n">
-        <v>7357000</v>
+        <v>8347736</v>
       </c>
       <c r="C7" s="32" t="n">
-        <v>169</v>
+        <v>8736</v>
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
@@ -4035,23 +4315,23 @@
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>214</v>
+        <v>9595</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>0.00365388115597387</v>
+        <v>0.1797442218180345</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>Jean-Luc Mélenchon</t>
+          <t>Marine Le Pen</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
-        <v>6439000</v>
-      </c>
-      <c r="C8" s="42" t="n">
-        <v>-1366</v>
+        <v>7357103</v>
+      </c>
+      <c r="C8" s="37" t="n">
+        <v>103</v>
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
@@ -4074,10 +4354,10 @@
         </is>
       </c>
       <c r="H8" s="37" t="n">
-        <v>859</v>
+        <v>317</v>
       </c>
       <c r="I8" s="39" t="n">
-        <v>0.02498443199392408</v>
+        <v>0.005412524889925052</v>
       </c>
     </row>
     <row r="9">
@@ -4087,10 +4367,10 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>4025800</v>
-      </c>
-      <c r="C9" s="40" t="n">
-        <v>-402601</v>
+        <v>5628466</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>402666</v>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
@@ -4113,23 +4393,23 @@
         </is>
       </c>
       <c r="H9" s="40" t="n">
-        <v>-402667</v>
+        <v>-1</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>-19.85080358714241</v>
+        <v>-3.097445320232595e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>Gabriel Attal</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
-        <v>1608400</v>
+        <v>1856332</v>
       </c>
       <c r="C10" s="37" t="n">
-        <v>1320</v>
+        <v>32</v>
       </c>
       <c r="D10" s="38" t="inlineStr">
         <is>
@@ -4152,23 +4432,23 @@
         </is>
       </c>
       <c r="H10" s="37" t="n">
-        <v>2318</v>
+        <v>1281</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.2507621308073915</v>
+        <v>0.06905470523452806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Édouard Philippe</t>
+          <t>Gabriel Attal</t>
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>1425300</v>
+        <v>1610984</v>
       </c>
       <c r="C11" s="32" t="n">
-        <v>186</v>
+        <v>2584</v>
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
@@ -4191,10 +4471,10 @@
         </is>
       </c>
       <c r="H11" s="32" t="n">
-        <v>249</v>
+        <v>4502</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>0.01747305885895223</v>
+        <v>0.4870280901185797</v>
       </c>
     </row>
     <row r="12">
@@ -4204,10 +4484,10 @@
         </is>
       </c>
       <c r="B12" s="36" t="n">
-        <v>944800</v>
-      </c>
-      <c r="C12" s="37" t="n">
-        <v>543</v>
+        <v>1522683</v>
+      </c>
+      <c r="C12" s="42" t="n">
+        <v>-117</v>
       </c>
       <c r="D12" s="38" t="inlineStr">
         <is>
@@ -4230,10 +4510,10 @@
         </is>
       </c>
       <c r="H12" s="37" t="n">
-        <v>382</v>
+        <v>265</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>0.04044819137287714</v>
+        <v>0.02356774793714767</v>
       </c>
     </row>
     <row r="13">
@@ -4243,10 +4523,10 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>577200</v>
-      </c>
-      <c r="C13" s="40" t="n">
-        <v>-303</v>
+        <v>658479</v>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>1279</v>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
@@ -4268,24 +4548,24 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="H13" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="54" t="n">
-        <v>0</v>
+      <c r="H13" s="32" t="n">
+        <v>879</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>0.1536176162181047</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>Bruno Retailleau</t>
+          <t>David Lisnard</t>
         </is>
       </c>
       <c r="B14" s="36" t="n">
-        <v>522200</v>
+        <v>575701</v>
       </c>
       <c r="C14" s="37" t="n">
-        <v>100</v>
+        <v>3798</v>
       </c>
       <c r="D14" s="38" t="inlineStr">
         <is>
@@ -4308,23 +4588,23 @@
         </is>
       </c>
       <c r="H14" s="37" t="n">
-        <v>516</v>
+        <v>7376</v>
       </c>
       <c r="I14" s="39" t="n">
-        <v>0.1181361954650351</v>
+        <v>1.341517755649524</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>David Lisnard</t>
+          <t>Bruno Retailleau</t>
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>470903</v>
-      </c>
-      <c r="C15" s="32" t="n">
-        <v>6803</v>
+        <v>521910</v>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>-290</v>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
@@ -4347,10 +4627,10 @@
         </is>
       </c>
       <c r="H15" s="32" t="n">
-        <v>3778</v>
+        <v>226</v>
       </c>
       <c r="I15" s="34" t="n">
-        <v>0.841753467387063</v>
+        <v>0.05174182204477074</v>
       </c>
     </row>
     <row r="16">
@@ -4360,10 +4640,10 @@
         </is>
       </c>
       <c r="B16" s="36" t="n">
-        <v>335400</v>
-      </c>
-      <c r="C16" s="37" t="n">
-        <v>287</v>
+        <v>335130</v>
+      </c>
+      <c r="C16" s="42" t="n">
+        <v>-270</v>
       </c>
       <c r="D16" s="38" t="inlineStr">
         <is>
@@ -4386,10 +4666,10 @@
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>282</v>
+        <v>12</v>
       </c>
       <c r="I16" s="39" t="n">
-        <v>0.08414946377097721</v>
+        <v>0.003580828245564049</v>
       </c>
     </row>
     <row r="18">
@@ -4456,7 +4736,7 @@
         </is>
       </c>
       <c r="B22" s="46" t="n">
-        <v>106000</v>
+        <v>105710</v>
       </c>
       <c r="C22" s="46" t="n">
         <v>213300</v>
@@ -4471,7 +4751,7 @@
         <v>84900</v>
       </c>
       <c r="G22" s="47" t="n">
-        <v>522200</v>
+        <v>521910</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -4481,22 +4761,22 @@
         </is>
       </c>
       <c r="B23" s="49" t="n">
-        <v>172703</v>
+        <v>175101</v>
       </c>
       <c r="C23" s="49" t="n">
-        <v>191900</v>
+        <v>192100</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>88000</v>
+        <v>89000</v>
       </c>
       <c r="E23" s="49" t="n">
         <v>101000</v>
       </c>
       <c r="F23" s="49" t="n">
-        <v>18300</v>
+        <v>18500</v>
       </c>
       <c r="G23" s="50" t="n">
-        <v>470903</v>
+        <v>575701</v>
       </c>
     </row>
     <row r="24">
@@ -4506,22 +4786,22 @@
         </is>
       </c>
       <c r="B24" s="46" t="n">
-        <v>462000</v>
+        <v>462184</v>
       </c>
       <c r="C24" s="46" t="n">
         <v>286700</v>
       </c>
       <c r="D24" s="46" t="n">
-        <v>178000</v>
+        <v>180000</v>
       </c>
       <c r="E24" s="46" t="n">
         <v>487000</v>
       </c>
       <c r="F24" s="46" t="n">
-        <v>681700</v>
+        <v>682100</v>
       </c>
       <c r="G24" s="47" t="n">
-        <v>1608400</v>
+        <v>1610984</v>
       </c>
     </row>
     <row r="25">
@@ -4531,7 +4811,7 @@
         </is>
       </c>
       <c r="B25" s="49" t="n">
-        <v>839000</v>
+        <v>847736</v>
       </c>
       <c r="C25" s="49" t="n">
         <v>2600000</v>
@@ -4548,7 +4828,7 @@
         <v>3000000</v>
       </c>
       <c r="G25" s="50" t="n">
-        <v>6439000</v>
+        <v>8347736</v>
       </c>
     </row>
     <row r="26">
@@ -4558,10 +4838,10 @@
         </is>
       </c>
       <c r="B26" s="46" t="n">
-        <v>1000000</v>
+        <v>1402566</v>
       </c>
       <c r="C26" s="46" t="n">
-        <v>625800</v>
+        <v>625900</v>
       </c>
       <c r="D26" s="46" t="n">
         <v>1200000</v>
@@ -4575,7 +4855,7 @@
         <v>2400000</v>
       </c>
       <c r="G26" s="47" t="n">
-        <v>4025800</v>
+        <v>5628466</v>
       </c>
     </row>
     <row r="27">
@@ -4585,7 +4865,7 @@
         </is>
       </c>
       <c r="B27" s="49" t="n">
-        <v>757000</v>
+        <v>757103</v>
       </c>
       <c r="C27" s="49" t="n">
         <v>3000000</v>
@@ -4602,7 +4882,7 @@
         <v>1500000</v>
       </c>
       <c r="G27" s="50" t="n">
-        <v>7357000</v>
+        <v>7357103</v>
       </c>
     </row>
     <row r="28">
@@ -4612,7 +4892,7 @@
         </is>
       </c>
       <c r="B28" s="46" t="n">
-        <v>356000</v>
+        <v>356879</v>
       </c>
       <c r="C28" s="46" t="n">
         <v>136200</v>
@@ -4626,10 +4906,10 @@
         </is>
       </c>
       <c r="F28" s="46" t="n">
-        <v>85000</v>
+        <v>85400</v>
       </c>
       <c r="G28" s="47" t="n">
-        <v>577200</v>
+        <v>658479</v>
       </c>
     </row>
     <row r="29">
@@ -4639,7 +4919,7 @@
         </is>
       </c>
       <c r="B29" s="49" t="n">
-        <v>637000</v>
+        <v>636883</v>
       </c>
       <c r="C29" s="49" t="n">
         <v>307800</v>
@@ -4647,10 +4927,8 @@
       <c r="D29" s="49" t="n">
         <v>180000</v>
       </c>
-      <c r="E29" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E29" s="49" t="n">
+        <v>398000</v>
       </c>
       <c r="F29" s="38" t="inlineStr">
         <is>
@@ -4658,7 +4936,7 @@
         </is>
       </c>
       <c r="G29" s="50" t="n">
-        <v>944800</v>
+        <v>1522683</v>
       </c>
     </row>
     <row r="30">
@@ -4668,7 +4946,7 @@
         </is>
       </c>
       <c r="B30" s="46" t="n">
-        <v>31000</v>
+        <v>30730</v>
       </c>
       <c r="C30" s="46" t="n">
         <v>205400</v>
@@ -4685,7 +4963,7 @@
         </is>
       </c>
       <c r="G30" s="47" t="n">
-        <v>335400</v>
+        <v>335130</v>
       </c>
     </row>
     <row r="31">
@@ -4695,16 +4973,16 @@
         </is>
       </c>
       <c r="B31" s="49" t="n">
-        <v>218000</v>
+        <v>218132</v>
       </c>
       <c r="C31" s="49" t="n">
-        <v>941300</v>
+        <v>941200</v>
       </c>
       <c r="D31" s="49" t="n">
         <v>266000</v>
       </c>
       <c r="E31" s="49" t="n">
-        <v>430000</v>
+        <v>431000</v>
       </c>
       <c r="F31" s="38" t="inlineStr">
         <is>
@@ -4712,7 +4990,7 @@
         </is>
       </c>
       <c r="G31" s="50" t="n">
-        <v>1425300</v>
+        <v>1856332</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -4800,13 +5078,13 @@
         </is>
       </c>
       <c r="C36" s="52" t="n">
-        <v>106000</v>
-      </c>
-      <c r="D36" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="54" t="n">
-        <v>0</v>
+        <v>105710</v>
+      </c>
+      <c r="D36" s="40" t="n">
+        <v>-290</v>
+      </c>
+      <c r="E36" s="41" t="n">
+        <v>-0.2735849056603734</v>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
@@ -4829,10 +5107,10 @@
         </is>
       </c>
       <c r="J36" s="32" t="n">
-        <v>416</v>
+        <v>126</v>
       </c>
       <c r="K36" s="34" t="n">
-        <v>0.3939990907713353</v>
+        <v>0.1193362630701689</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -4849,11 +5127,11 @@
       <c r="C37" s="52" t="n">
         <v>213300</v>
       </c>
-      <c r="D37" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="E37" s="34" t="n">
-        <v>0.046904315197005</v>
+      <c r="D37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="51" t="inlineStr">
         <is>
@@ -4998,15 +5276,11 @@
       <c r="C40" s="52" t="n">
         <v>84900</v>
       </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E40" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D40" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
@@ -5051,13 +5325,13 @@
         </is>
       </c>
       <c r="C41" s="56" t="n">
-        <v>522200</v>
-      </c>
-      <c r="D41" s="57" t="n">
-        <v>100</v>
-      </c>
-      <c r="E41" s="58" t="n">
-        <v>0.02287282708142158</v>
+        <v>521910</v>
+      </c>
+      <c r="D41" s="59" t="n">
+        <v>-290</v>
+      </c>
+      <c r="E41" s="60" t="n">
+        <v>-0.05553427805438105</v>
       </c>
       <c r="F41" s="55" t="inlineStr">
         <is>
@@ -5080,10 +5354,10 @@
         </is>
       </c>
       <c r="J41" s="57" t="n">
-        <v>516</v>
+        <v>226</v>
       </c>
       <c r="K41" s="58" t="n">
-        <v>0.1181361954650351</v>
+        <v>0.05174182204477074</v>
       </c>
     </row>
     <row r="42">
@@ -5098,13 +5372,13 @@
         </is>
       </c>
       <c r="C42" s="52" t="n">
-        <v>172703</v>
+        <v>175101</v>
       </c>
       <c r="D42" s="32" t="n">
-        <v>6703</v>
+        <v>2398</v>
       </c>
       <c r="E42" s="34" t="n">
-        <v>4.037951807228923</v>
+        <v>1.388510911796548</v>
       </c>
       <c r="F42" s="51" t="inlineStr">
         <is>
@@ -5127,10 +5401,10 @@
         </is>
       </c>
       <c r="J42" s="32" t="n">
-        <v>3678</v>
+        <v>6076</v>
       </c>
       <c r="K42" s="34" t="n">
-        <v>2.176009466055318</v>
+        <v>3.59473450672978</v>
       </c>
     </row>
     <row r="43">
@@ -5145,13 +5419,13 @@
         </is>
       </c>
       <c r="C43" s="52" t="n">
-        <v>191900</v>
+        <v>192100</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="34" t="n">
-        <v>0.05213764337852478</v>
+        <v>0.1042209484106271</v>
       </c>
       <c r="F43" s="51" t="inlineStr">
         <is>
@@ -5174,10 +5448,10 @@
         </is>
       </c>
       <c r="J43" s="32" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K43" s="34" t="n">
-        <v>0.05213764337852478</v>
+        <v>0.1564129301355521</v>
       </c>
     </row>
     <row r="44">
@@ -5192,13 +5466,13 @@
         </is>
       </c>
       <c r="C44" s="52" t="n">
-        <v>88000</v>
-      </c>
-      <c r="D44" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="54" t="n">
-        <v>0</v>
+        <v>89000</v>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="34" t="n">
+        <v>1.136363636363646</v>
       </c>
       <c r="F44" s="51" t="inlineStr">
         <is>
@@ -5220,11 +5494,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J44" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="54" t="n">
-        <v>0</v>
+      <c r="J44" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K44" s="34" t="n">
+        <v>1.136363636363646</v>
       </c>
     </row>
     <row r="45">
@@ -5271,15 +5545,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J45" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K45" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J45" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5294,17 +5564,13 @@
         </is>
       </c>
       <c r="C46" s="52" t="n">
-        <v>18300</v>
-      </c>
-      <c r="D46" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E46" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>18500</v>
+      </c>
+      <c r="D46" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="E46" s="34" t="n">
+        <v>1.092896174863389</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
@@ -5349,13 +5615,13 @@
         </is>
       </c>
       <c r="C47" s="56" t="n">
-        <v>470903</v>
+        <v>575701</v>
       </c>
       <c r="D47" s="57" t="n">
-        <v>6803</v>
+        <v>3798</v>
       </c>
       <c r="E47" s="58" t="n">
-        <v>1.52602063705698</v>
+        <v>0.8065355285483466</v>
       </c>
       <c r="F47" s="55" t="inlineStr">
         <is>
@@ -5378,10 +5644,10 @@
         </is>
       </c>
       <c r="J47" s="57" t="n">
-        <v>3778</v>
+        <v>7376</v>
       </c>
       <c r="K47" s="58" t="n">
-        <v>0.841753467387063</v>
+        <v>1.341517755649524</v>
       </c>
     </row>
     <row r="48">
@@ -5396,13 +5662,13 @@
         </is>
       </c>
       <c r="C48" s="52" t="n">
-        <v>462000</v>
+        <v>462184</v>
       </c>
       <c r="D48" s="32" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="E48" s="34" t="n">
-        <v>0.04764173415912065</v>
+        <v>0.03982683982683977</v>
       </c>
       <c r="F48" s="51" t="inlineStr">
         <is>
@@ -5425,10 +5691,10 @@
         </is>
       </c>
       <c r="J48" s="32" t="n">
-        <v>218</v>
+        <v>402</v>
       </c>
       <c r="K48" s="34" t="n">
-        <v>0.04720842302212702</v>
+        <v>0.08705406447198083</v>
       </c>
     </row>
     <row r="49">
@@ -5445,11 +5711,11 @@
       <c r="C49" s="52" t="n">
         <v>286700</v>
       </c>
-      <c r="D49" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="E49" s="34" t="n">
-        <v>0.03489183531053541</v>
+      <c r="D49" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="51" t="inlineStr">
         <is>
@@ -5490,13 +5756,13 @@
         </is>
       </c>
       <c r="C50" s="52" t="n">
-        <v>178000</v>
+        <v>180000</v>
       </c>
       <c r="D50" s="32" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E50" s="34" t="n">
-        <v>0.5649717514124353</v>
+        <v>1.12359550561798</v>
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
@@ -5519,10 +5785,10 @@
         </is>
       </c>
       <c r="J50" s="32" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="K50" s="34" t="n">
-        <v>1.136363636363646</v>
+        <v>2.272727272727271</v>
       </c>
     </row>
     <row r="51">
@@ -5592,17 +5858,13 @@
         </is>
       </c>
       <c r="C52" s="52" t="n">
-        <v>681700</v>
-      </c>
-      <c r="D52" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E52" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>682100</v>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>400</v>
+      </c>
+      <c r="E52" s="34" t="n">
+        <v>0.05867683731846096</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
@@ -5647,13 +5909,13 @@
         </is>
       </c>
       <c r="C53" s="56" t="n">
-        <v>1608400</v>
+        <v>1610984</v>
       </c>
       <c r="D53" s="57" t="n">
-        <v>1320</v>
+        <v>2584</v>
       </c>
       <c r="E53" s="58" t="n">
-        <v>0.1426441029630965</v>
+        <v>0.16065655309625</v>
       </c>
       <c r="F53" s="55" t="inlineStr">
         <is>
@@ -5676,10 +5938,10 @@
         </is>
       </c>
       <c r="J53" s="57" t="n">
-        <v>2318</v>
+        <v>4502</v>
       </c>
       <c r="K53" s="58" t="n">
-        <v>0.2507621308073915</v>
+        <v>0.4870280901185797</v>
       </c>
     </row>
     <row r="54">
@@ -5694,13 +5956,13 @@
         </is>
       </c>
       <c r="C54" s="52" t="n">
-        <v>839000</v>
-      </c>
-      <c r="D54" s="40" t="n">
-        <v>-1366</v>
-      </c>
-      <c r="E54" s="41" t="n">
-        <v>-0.1625482230361519</v>
+        <v>847736</v>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>8736</v>
+      </c>
+      <c r="E54" s="34" t="n">
+        <v>1.041239570917751</v>
       </c>
       <c r="F54" s="51" t="inlineStr">
         <is>
@@ -5723,10 +5985,10 @@
         </is>
       </c>
       <c r="J54" s="32" t="n">
-        <v>859</v>
+        <v>9595</v>
       </c>
       <c r="K54" s="34" t="n">
-        <v>0.1024887220646642</v>
+        <v>1.144795446112279</v>
       </c>
     </row>
     <row r="55">
@@ -5820,15 +6082,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J56" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K56" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J56" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5845,15 +6103,11 @@
       <c r="C57" s="52" t="n">
         <v>3000000</v>
       </c>
-      <c r="D57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D57" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="51" t="inlineStr">
         <is>
@@ -5898,13 +6152,13 @@
         </is>
       </c>
       <c r="C58" s="56" t="n">
-        <v>6439000</v>
-      </c>
-      <c r="D58" s="59" t="n">
-        <v>-1366</v>
-      </c>
-      <c r="E58" s="60" t="n">
-        <v>-0.03970507788997324</v>
+        <v>8347736</v>
+      </c>
+      <c r="D58" s="57" t="n">
+        <v>8736</v>
+      </c>
+      <c r="E58" s="58" t="n">
+        <v>0.1356732411865291</v>
       </c>
       <c r="F58" s="55" t="inlineStr">
         <is>
@@ -5927,10 +6181,10 @@
         </is>
       </c>
       <c r="J58" s="57" t="n">
-        <v>859</v>
+        <v>9595</v>
       </c>
       <c r="K58" s="58" t="n">
-        <v>0.02498443199392408</v>
+        <v>0.1797442218180345</v>
       </c>
     </row>
     <row r="59">
@@ -5945,13 +6199,13 @@
         </is>
       </c>
       <c r="C59" s="52" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D59" s="40" t="n">
-        <v>-402601</v>
-      </c>
-      <c r="E59" s="41" t="n">
-        <v>-28.70388656503168</v>
+        <v>1402566</v>
+      </c>
+      <c r="D59" s="32" t="n">
+        <v>402566</v>
+      </c>
+      <c r="E59" s="34" t="n">
+        <v>40.2566</v>
       </c>
       <c r="F59" s="51" t="inlineStr">
         <is>
@@ -5974,10 +6228,10 @@
         </is>
       </c>
       <c r="J59" s="40" t="n">
-        <v>-402767</v>
+        <v>-201</v>
       </c>
       <c r="K59" s="41" t="n">
-        <v>-28.7123235719118</v>
+        <v>-0.01432882296205085</v>
       </c>
     </row>
     <row r="60">
@@ -5992,13 +6246,13 @@
         </is>
       </c>
       <c r="C60" s="52" t="n">
-        <v>625800</v>
-      </c>
-      <c r="D60" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="54" t="n">
-        <v>0</v>
+        <v>625900</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" s="34" t="n">
+        <v>0.0159795461808887</v>
       </c>
       <c r="F60" s="51" t="inlineStr">
         <is>
@@ -6021,10 +6275,10 @@
         </is>
       </c>
       <c r="J60" s="32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K60" s="34" t="n">
-        <v>0.01598210004793987</v>
+        <v>0.03196420009590195</v>
       </c>
     </row>
     <row r="61">
@@ -6071,15 +6325,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J61" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K61" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -6096,15 +6346,11 @@
       <c r="C62" s="52" t="n">
         <v>2400000</v>
       </c>
-      <c r="D62" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E62" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D62" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="51" t="inlineStr">
         <is>
@@ -6149,13 +6395,13 @@
         </is>
       </c>
       <c r="C63" s="56" t="n">
-        <v>4025800</v>
-      </c>
-      <c r="D63" s="59" t="n">
-        <v>-402601</v>
-      </c>
-      <c r="E63" s="60" t="n">
-        <v>-19.84819569700469</v>
+        <v>5628466</v>
+      </c>
+      <c r="D63" s="57" t="n">
+        <v>402666</v>
+      </c>
+      <c r="E63" s="58" t="n">
+        <v>10.00213622137216</v>
       </c>
       <c r="F63" s="55" t="inlineStr">
         <is>
@@ -6178,10 +6424,10 @@
         </is>
       </c>
       <c r="J63" s="59" t="n">
-        <v>-402667</v>
+        <v>-1</v>
       </c>
       <c r="K63" s="60" t="n">
-        <v>-19.85080358714241</v>
+        <v>-3.097445320232595e-05</v>
       </c>
     </row>
     <row r="64">
@@ -6196,13 +6442,13 @@
         </is>
       </c>
       <c r="C64" s="52" t="n">
-        <v>757000</v>
+        <v>757103</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="E64" s="34" t="n">
-        <v>0.02232995212934075</v>
+        <v>0.01360634081901679</v>
       </c>
       <c r="F64" s="51" t="inlineStr">
         <is>
@@ -6225,10 +6471,10 @@
         </is>
       </c>
       <c r="J64" s="32" t="n">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="K64" s="34" t="n">
-        <v>0.02827747870599584</v>
+        <v>0.04188766705515157</v>
       </c>
     </row>
     <row r="65">
@@ -6339,15 +6585,11 @@
       <c r="C67" s="52" t="n">
         <v>1500000</v>
       </c>
-      <c r="D67" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E67" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D67" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="51" t="inlineStr">
         <is>
@@ -6392,13 +6634,13 @@
         </is>
       </c>
       <c r="C68" s="56" t="n">
-        <v>7357000</v>
+        <v>7357103</v>
       </c>
       <c r="D68" s="57" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="E68" s="58" t="n">
-        <v>0.002885519489970179</v>
+        <v>0.001400027184983443</v>
       </c>
       <c r="F68" s="55" t="inlineStr">
         <is>
@@ -6421,10 +6663,10 @@
         </is>
       </c>
       <c r="J68" s="57" t="n">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="K68" s="58" t="n">
-        <v>0.00365388115597387</v>
+        <v>0.005412524889925052</v>
       </c>
     </row>
     <row r="69">
@@ -6439,13 +6681,13 @@
         </is>
       </c>
       <c r="C69" s="52" t="n">
-        <v>356000</v>
-      </c>
-      <c r="D69" s="40" t="n">
-        <v>-303</v>
-      </c>
-      <c r="E69" s="41" t="n">
-        <v>-0.08503998001700985</v>
+        <v>356879</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>879</v>
+      </c>
+      <c r="E69" s="34" t="n">
+        <v>0.2469101123595552</v>
       </c>
       <c r="F69" s="51" t="inlineStr">
         <is>
@@ -6467,11 +6709,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J69" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="54" t="n">
-        <v>0</v>
+      <c r="J69" s="32" t="n">
+        <v>879</v>
+      </c>
+      <c r="K69" s="34" t="n">
+        <v>0.2469101123595552</v>
       </c>
     </row>
     <row r="70">
@@ -6565,15 +6807,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J71" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K71" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J71" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6588,17 +6826,13 @@
         </is>
       </c>
       <c r="C72" s="52" t="n">
-        <v>85000</v>
-      </c>
-      <c r="D72" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E72" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>85400</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>400</v>
+      </c>
+      <c r="E72" s="34" t="n">
+        <v>0.4705882352941115</v>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
@@ -6643,13 +6877,13 @@
         </is>
       </c>
       <c r="C73" s="56" t="n">
-        <v>577200</v>
-      </c>
-      <c r="D73" s="59" t="n">
-        <v>-303</v>
-      </c>
-      <c r="E73" s="60" t="n">
-        <v>-0.06152246788344584</v>
+        <v>658479</v>
+      </c>
+      <c r="D73" s="57" t="n">
+        <v>1279</v>
+      </c>
+      <c r="E73" s="58" t="n">
+        <v>0.2215869715869623</v>
       </c>
       <c r="F73" s="55" t="inlineStr">
         <is>
@@ -6671,11 +6905,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J73" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="65" t="n">
-        <v>0</v>
+      <c r="J73" s="57" t="n">
+        <v>879</v>
+      </c>
+      <c r="K73" s="58" t="n">
+        <v>0.1536176162181047</v>
       </c>
     </row>
     <row r="74">
@@ -6690,13 +6924,13 @@
         </is>
       </c>
       <c r="C74" s="52" t="n">
-        <v>637000</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>543</v>
-      </c>
-      <c r="E74" s="34" t="n">
-        <v>0.08531605434460854</v>
+        <v>636883</v>
+      </c>
+      <c r="D74" s="40" t="n">
+        <v>-117</v>
+      </c>
+      <c r="E74" s="41" t="n">
+        <v>-0.01836734693877462</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
@@ -6719,10 +6953,10 @@
         </is>
       </c>
       <c r="J74" s="32" t="n">
-        <v>482</v>
+        <v>365</v>
       </c>
       <c r="K74" s="34" t="n">
-        <v>0.07572448854549219</v>
+        <v>0.05734323302719613</v>
       </c>
     </row>
     <row r="75">
@@ -6816,109 +7050,113 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J76" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K76" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J76" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="55" t="inlineStr">
+      <c r="A77" s="51" t="inlineStr">
         <is>
           <t>Raphaël Glucksmann</t>
         </is>
       </c>
-      <c r="B77" s="55" t="inlineStr">
+      <c r="B77" s="51" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="C77" s="52" t="n">
+        <v>398000</v>
+      </c>
+      <c r="D77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K77" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="55" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="B78" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C77" s="56" t="n">
-        <v>944800</v>
-      </c>
-      <c r="D77" s="57" t="n">
-        <v>543</v>
-      </c>
-      <c r="E77" s="58" t="n">
-        <v>0.05750553080359211</v>
-      </c>
-      <c r="F77" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G77" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H77" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I77" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J77" s="57" t="n">
-        <v>382</v>
-      </c>
-      <c r="K77" s="58" t="n">
-        <v>0.04044819137287714</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="51" t="inlineStr">
-        <is>
-          <t>Xavier Bertrand</t>
-        </is>
-      </c>
-      <c r="B78" s="51" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C78" s="52" t="n">
-        <v>31000</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>287</v>
-      </c>
-      <c r="E78" s="34" t="n">
-        <v>0.934457721486015</v>
-      </c>
-      <c r="F78" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G78" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H78" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I78" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J78" s="32" t="n">
-        <v>282</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>0.9180285174816172</v>
+      <c r="C78" s="56" t="n">
+        <v>1522683</v>
+      </c>
+      <c r="D78" s="59" t="n">
+        <v>-117</v>
+      </c>
+      <c r="E78" s="60" t="n">
+        <v>-0.01238357324301331</v>
+      </c>
+      <c r="F78" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G78" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H78" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I78" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J78" s="57" t="n">
+        <v>265</v>
+      </c>
+      <c r="K78" s="58" t="n">
+        <v>0.02356774793714767</v>
       </c>
     </row>
     <row r="79">
@@ -6929,17 +7167,17 @@
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C79" s="52" t="n">
-        <v>205400</v>
-      </c>
-      <c r="D79" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="54" t="n">
-        <v>0</v>
+        <v>30730</v>
+      </c>
+      <c r="D79" s="40" t="n">
+        <v>-270</v>
+      </c>
+      <c r="E79" s="41" t="n">
+        <v>-0.87096774193548</v>
       </c>
       <c r="F79" s="51" t="inlineStr">
         <is>
@@ -6961,11 +7199,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J79" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="54" t="n">
-        <v>0</v>
+      <c r="J79" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="K79" s="34" t="n">
+        <v>0.03906504329709293</v>
       </c>
     </row>
     <row r="80">
@@ -6976,11 +7214,11 @@
       </c>
       <c r="B80" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C80" s="52" t="n">
-        <v>99000</v>
+        <v>205400</v>
       </c>
       <c r="D80" s="53" t="n">
         <v>0</v>
@@ -7023,145 +7261,145 @@
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C81" s="52" t="n">
+        <v>99000</v>
+      </c>
+      <c r="D81" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G81" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H81" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I81" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J81" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="51" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="B82" s="51" t="inlineStr">
+        <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C81" s="52" t="n">
+      <c r="C82" s="52" t="n">
         <v>44000</v>
       </c>
-      <c r="D81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="55" t="inlineStr">
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K82" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="55" t="inlineStr">
         <is>
           <t>Xavier Bertrand</t>
         </is>
       </c>
-      <c r="B82" s="55" t="inlineStr">
+      <c r="B83" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C82" s="56" t="n">
-        <v>335400</v>
-      </c>
-      <c r="D82" s="57" t="n">
-        <v>287</v>
-      </c>
-      <c r="E82" s="58" t="n">
-        <v>0.08564275333990956</v>
-      </c>
-      <c r="F82" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G82" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H82" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I82" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J82" s="57" t="n">
-        <v>282</v>
-      </c>
-      <c r="K82" s="58" t="n">
-        <v>0.08414946377097721</v>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="51" t="inlineStr">
-        <is>
-          <t>Édouard Philippe</t>
-        </is>
-      </c>
-      <c r="B83" s="51" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C83" s="52" t="n">
-        <v>218000</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>186</v>
-      </c>
-      <c r="E83" s="34" t="n">
-        <v>0.08539395998421462</v>
-      </c>
-      <c r="F83" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G83" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H83" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I83" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J83" s="32" t="n">
-        <v>149</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>0.06839537114817773</v>
+      <c r="C83" s="56" t="n">
+        <v>335130</v>
+      </c>
+      <c r="D83" s="59" t="n">
+        <v>-270</v>
+      </c>
+      <c r="E83" s="60" t="n">
+        <v>-0.0805008944543828</v>
+      </c>
+      <c r="F83" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G83" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H83" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I83" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J83" s="57" t="n">
+        <v>12</v>
+      </c>
+      <c r="K83" s="58" t="n">
+        <v>0.003580828245564049</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -7172,17 +7410,17 @@
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C84" s="52" t="n">
-        <v>941300</v>
-      </c>
-      <c r="D84" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="54" t="n">
-        <v>0</v>
+        <v>218132</v>
+      </c>
+      <c r="D84" s="32" t="n">
+        <v>132</v>
+      </c>
+      <c r="E84" s="34" t="n">
+        <v>0.0605504587156025</v>
       </c>
       <c r="F84" s="51" t="inlineStr">
         <is>
@@ -7205,10 +7443,10 @@
         </is>
       </c>
       <c r="J84" s="32" t="n">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="K84" s="34" t="n">
-        <v>0.0106247343816479</v>
+        <v>0.1289872435747297</v>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
@@ -7219,17 +7457,17 @@
       </c>
       <c r="B85" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C85" s="52" t="n">
-        <v>266000</v>
-      </c>
-      <c r="D85" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="54" t="n">
-        <v>0</v>
+        <v>941200</v>
+      </c>
+      <c r="D85" s="40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E85" s="41" t="n">
+        <v>-0.01062360565176057</v>
       </c>
       <c r="F85" s="51" t="inlineStr">
         <is>
@@ -7266,539 +7504,582 @@
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C86" s="52" t="n">
+        <v>266000</v>
+      </c>
+      <c r="D86" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G86" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H86" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I86" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J86" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="51" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C86" s="52" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="55" t="inlineStr">
+      <c r="C87" s="52" t="n">
+        <v>431000</v>
+      </c>
+      <c r="D87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J87" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K87" s="34" t="n">
+        <v>0.2325581395348886</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="55" t="inlineStr">
         <is>
           <t>Édouard Philippe</t>
         </is>
       </c>
-      <c r="B87" s="55" t="inlineStr">
+      <c r="B88" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C87" s="56" t="n">
-        <v>1425300</v>
-      </c>
-      <c r="D87" s="57" t="n">
-        <v>186</v>
-      </c>
-      <c r="E87" s="58" t="n">
-        <v>0.01305158745195101</v>
-      </c>
-      <c r="F87" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G87" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H87" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I87" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J87" s="57" t="n">
-        <v>249</v>
-      </c>
-      <c r="K87" s="58" t="n">
-        <v>0.01747305885895223</v>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1"/>
+      <c r="C88" s="56" t="n">
+        <v>1856332</v>
+      </c>
+      <c r="D88" s="57" t="n">
+        <v>32</v>
+      </c>
+      <c r="E88" s="58" t="n">
+        <v>0.002245141373746762</v>
+      </c>
+      <c r="F88" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G88" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H88" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I88" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J88" s="57" t="n">
+        <v>1281</v>
+      </c>
+      <c r="K88" s="58" t="n">
+        <v>0.06905470523452806</v>
+      </c>
+    </row>
     <row r="89" ht="30" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="27" t="inlineStr">
+    <row r="90" ht="20" customHeight="1"/>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
         <is>
           <t>CLASSEMENT CROISSANCE 7 JOURS</t>
         </is>
       </c>
-      <c r="B90" s="28" t="n"/>
-      <c r="C90" s="28" t="n"/>
-      <c r="D90" s="28" t="n"/>
-      <c r="E90" s="28" t="n"/>
-      <c r="F90" s="28" t="n"/>
-      <c r="G90" s="28" t="n"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="29" t="inlineStr">
+      <c r="B91" s="28" t="n"/>
+      <c r="C91" s="28" t="n"/>
+      <c r="D91" s="28" t="n"/>
+      <c r="E91" s="28" t="n"/>
+      <c r="F91" s="28" t="n"/>
+      <c r="G91" s="28" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B91" s="29" t="inlineStr">
+      <c r="B92" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C91" s="29" t="inlineStr">
+      <c r="C92" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D91" s="29" t="inlineStr">
+      <c r="D92" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E91" s="29" t="inlineStr"/>
-      <c r="F91" s="29" t="inlineStr">
+      <c r="E92" s="29" t="inlineStr"/>
+      <c r="F92" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G91" s="29" t="inlineStr">
+      <c r="G92" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H91" s="29" t="inlineStr">
+      <c r="H92" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="13" t="inlineStr">
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="13" t="inlineStr">
         <is>
           <t>Pas encore assez d'historique pour cette periode.</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30" customHeight="1"/>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="27" t="inlineStr">
+    <row r="94" ht="20" customHeight="1"/>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
         <is>
           <t>CLASSEMENT CROISSANCE 30 JOURS</t>
         </is>
       </c>
-      <c r="B94" s="28" t="n"/>
-      <c r="C94" s="28" t="n"/>
-      <c r="D94" s="28" t="n"/>
-      <c r="E94" s="28" t="n"/>
-      <c r="F94" s="28" t="n"/>
-      <c r="G94" s="28" t="n"/>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="29" t="inlineStr">
+      <c r="B95" s="28" t="n"/>
+      <c r="C95" s="28" t="n"/>
+      <c r="D95" s="28" t="n"/>
+      <c r="E95" s="28" t="n"/>
+      <c r="F95" s="28" t="n"/>
+      <c r="G95" s="28" t="n"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B95" s="29" t="inlineStr">
+      <c r="B96" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C95" s="29" t="inlineStr">
+      <c r="C96" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D95" s="29" t="inlineStr">
+      <c r="D96" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E95" s="29" t="inlineStr"/>
-      <c r="F95" s="29" t="inlineStr">
+      <c r="E96" s="29" t="inlineStr"/>
+      <c r="F96" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G95" s="29" t="inlineStr">
+      <c r="G96" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H95" s="29" t="inlineStr">
+      <c r="H96" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="13" t="inlineStr">
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>Pas encore assez d'historique pour cette periode.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="30" customHeight="1"/>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
+    <row r="98" ht="20" customHeight="1"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
         <is>
           <t>CLASSEMENT CROISSANCE DEPUIS LE DEBUT DU SUIVI</t>
         </is>
       </c>
-      <c r="B98" s="28" t="n"/>
-      <c r="C98" s="28" t="n"/>
-      <c r="D98" s="28" t="n"/>
-      <c r="E98" s="28" t="n"/>
-      <c r="F98" s="28" t="n"/>
-      <c r="G98" s="28" t="n"/>
-    </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="29" t="inlineStr">
+      <c r="B99" s="28" t="n"/>
+      <c r="C99" s="28" t="n"/>
+      <c r="D99" s="28" t="n"/>
+      <c r="E99" s="28" t="n"/>
+      <c r="F99" s="28" t="n"/>
+      <c r="G99" s="28" t="n"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B99" s="29" t="inlineStr">
+      <c r="B100" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C99" s="29" t="inlineStr">
+      <c r="C100" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D99" s="29" t="inlineStr">
+      <c r="D100" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E99" s="29" t="inlineStr"/>
-      <c r="F99" s="29" t="inlineStr">
+      <c r="E100" s="29" t="inlineStr"/>
+      <c r="F100" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G99" s="29" t="inlineStr">
+      <c r="G100" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H99" s="29" t="inlineStr">
+      <c r="H100" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="B100" s="45" t="inlineStr">
-        <is>
-          <t>David Lisnard</t>
-        </is>
-      </c>
-      <c r="C100" s="34" t="n">
-        <v>0.841753467387063</v>
-      </c>
-      <c r="D100" s="32" t="n">
-        <v>3778</v>
-      </c>
-      <c r="F100" s="45" t="inlineStr">
-        <is>
-          <t>David Lisnard</t>
-        </is>
-      </c>
-      <c r="G100" s="32" t="n">
-        <v>3778</v>
-      </c>
-      <c r="H100" s="34" t="n">
-        <v>0.841753467387063</v>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B101" s="45" t="inlineStr">
         <is>
-          <t>Gabriel Attal</t>
+          <t>David Lisnard</t>
         </is>
       </c>
       <c r="C101" s="34" t="n">
-        <v>0.2507621308073915</v>
+        <v>1.341517755649524</v>
       </c>
       <c r="D101" s="32" t="n">
-        <v>2318</v>
+        <v>7376</v>
       </c>
       <c r="F101" s="45" t="inlineStr">
         <is>
-          <t>Gabriel Attal</t>
+          <t>Jean-Luc Mélenchon</t>
         </is>
       </c>
       <c r="G101" s="32" t="n">
-        <v>2318</v>
+        <v>9595</v>
       </c>
       <c r="H101" s="34" t="n">
-        <v>0.2507621308073915</v>
+        <v>0.1797442218180345</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B102" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C102" s="34" t="n">
+        <v>0.4870280901185797</v>
+      </c>
+      <c r="D102" s="32" t="n">
+        <v>4502</v>
+      </c>
+      <c r="F102" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="G102" s="32" t="n">
+        <v>7376</v>
+      </c>
+      <c r="H102" s="34" t="n">
+        <v>1.341517755649524</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="B102" s="45" t="inlineStr">
-        <is>
-          <t>Bruno Retailleau</t>
-        </is>
-      </c>
-      <c r="C102" s="34" t="n">
-        <v>0.1181361954650351</v>
-      </c>
-      <c r="D102" s="32" t="n">
-        <v>516</v>
-      </c>
-      <c r="F102" s="45" t="inlineStr">
+      <c r="B103" s="45" t="inlineStr">
         <is>
           <t>Jean-Luc Mélenchon</t>
         </is>
       </c>
-      <c r="G102" s="32" t="n">
-        <v>859</v>
-      </c>
-      <c r="H102" s="34" t="n">
-        <v>0.02498443199392408</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="B103" s="63" t="inlineStr">
-        <is>
-          <t>Xavier Bertrand</t>
-        </is>
-      </c>
       <c r="C103" s="34" t="n">
-        <v>0.08414946377097721</v>
+        <v>0.1797442218180345</v>
       </c>
       <c r="D103" s="32" t="n">
-        <v>282</v>
-      </c>
-      <c r="F103" s="63" t="inlineStr">
-        <is>
-          <t>Bruno Retailleau</t>
+        <v>9595</v>
+      </c>
+      <c r="F103" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
         </is>
       </c>
       <c r="G103" s="32" t="n">
-        <v>516</v>
+        <v>4502</v>
       </c>
       <c r="H103" s="34" t="n">
-        <v>0.1181361954650351</v>
+        <v>0.4870280901185797</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104" s="63" t="inlineStr">
         <is>
-          <t>Raphaël Glucksmann</t>
+          <t>Marine Tondelier</t>
         </is>
       </c>
       <c r="C104" s="34" t="n">
-        <v>0.04044819137287714</v>
+        <v>0.1536176162181047</v>
       </c>
       <c r="D104" s="32" t="n">
-        <v>382</v>
+        <v>879</v>
       </c>
       <c r="F104" s="63" t="inlineStr">
         <is>
-          <t>Raphaël Glucksmann</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="G104" s="32" t="n">
-        <v>382</v>
+        <v>1281</v>
       </c>
       <c r="H104" s="34" t="n">
-        <v>0.04044819137287714</v>
+        <v>0.06905470523452806</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B105" s="63" t="inlineStr">
         <is>
-          <t>Jean-Luc Mélenchon</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="C105" s="34" t="n">
-        <v>0.02498443199392408</v>
+        <v>0.06905470523452806</v>
       </c>
       <c r="D105" s="32" t="n">
-        <v>859</v>
+        <v>1281</v>
       </c>
       <c r="F105" s="63" t="inlineStr">
         <is>
-          <t>Xavier Bertrand</t>
+          <t>Marine Tondelier</t>
         </is>
       </c>
       <c r="G105" s="32" t="n">
-        <v>282</v>
+        <v>879</v>
       </c>
       <c r="H105" s="34" t="n">
-        <v>0.08414946377097721</v>
+        <v>0.1536176162181047</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106" s="63" t="inlineStr">
         <is>
-          <t>Édouard Philippe</t>
+          <t>Bruno Retailleau</t>
         </is>
       </c>
       <c r="C106" s="34" t="n">
-        <v>0.01747305885895223</v>
+        <v>0.05174182204477074</v>
       </c>
       <c r="D106" s="32" t="n">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="F106" s="63" t="inlineStr">
         <is>
-          <t>Édouard Philippe</t>
+          <t>Marine Le Pen</t>
         </is>
       </c>
       <c r="G106" s="32" t="n">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="H106" s="34" t="n">
-        <v>0.01747305885895223</v>
+        <v>0.005412524889925052</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B107" s="63" t="inlineStr">
         <is>
-          <t>Marine Le Pen</t>
+          <t>Raphaël Glucksmann</t>
         </is>
       </c>
       <c r="C107" s="34" t="n">
-        <v>0.00365388115597387</v>
+        <v>0.02356774793714767</v>
       </c>
       <c r="D107" s="32" t="n">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="F107" s="63" t="inlineStr">
         <is>
-          <t>Marine Le Pen</t>
+          <t>Raphaël Glucksmann</t>
         </is>
       </c>
       <c r="G107" s="32" t="n">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="H107" s="34" t="n">
-        <v>0.00365388115597387</v>
+        <v>0.02356774793714767</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B108" s="63" t="inlineStr">
         <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
-      <c r="C108" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="53" t="n">
-        <v>0</v>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C108" s="34" t="n">
+        <v>0.005412524889925052</v>
+      </c>
+      <c r="D108" s="32" t="n">
+        <v>317</v>
       </c>
       <c r="F108" s="63" t="inlineStr">
         <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
-      <c r="G108" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="54" t="n">
-        <v>0</v>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="G108" s="32" t="n">
+        <v>226</v>
+      </c>
+      <c r="H108" s="34" t="n">
+        <v>0.05174182204477074</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B109" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C109" s="34" t="n">
+        <v>0.003580828245564049</v>
+      </c>
+      <c r="D109" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F109" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="G109" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H109" s="34" t="n">
+        <v>0.003580828245564049</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="B109" s="63" t="inlineStr">
+      <c r="B110" s="63" t="inlineStr">
         <is>
           <t>Jordan Bardella</t>
         </is>
       </c>
-      <c r="C109" s="41" t="n">
-        <v>-19.85080358714241</v>
-      </c>
-      <c r="D109" s="40" t="n">
-        <v>-402667</v>
-      </c>
-      <c r="F109" s="63" t="inlineStr">
+      <c r="C110" s="41" t="n">
+        <v>-3.097445320232595e-05</v>
+      </c>
+      <c r="D110" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F110" s="63" t="inlineStr">
         <is>
           <t>Jordan Bardella</t>
         </is>
       </c>
-      <c r="G109" s="40" t="n">
-        <v>-402667</v>
-      </c>
-      <c r="H109" s="41" t="n">
-        <v>-19.85080358714241</v>
+      <c r="G110" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H110" s="41" t="n">
+        <v>-3.097445320232595e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7858,7 +8139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG5"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8175,31 +8456,31 @@
         <v>436784</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>448825</v>
+        <v>549825</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>924382</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3438141</v>
+        <v>5338141</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2028467</v>
+        <v>3228467</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>5856786</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>492200</v>
+        <v>572200</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>944418</v>
+        <v>1124418</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>335118</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1425051</v>
+        <v>1855051</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -8322,31 +8603,31 @@
         <v>437200</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>445800</v>
+        <v>546800</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>925380</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3440366</v>
+        <v>5340366</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2028401</v>
+        <v>3228401</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5856831</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>492503</v>
+        <v>572503</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>944257</v>
+        <v>1124257</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>335113</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1425114</v>
+        <v>1855114</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -8357,31 +8638,31 @@
         <v>1000.95</v>
       </c>
       <c r="O4" s="14" t="n">
-        <v>993.26</v>
+        <v>994.5</v>
       </c>
       <c r="P4" s="14" t="n">
         <v>1001.08</v>
       </c>
       <c r="Q4" s="14" t="n">
-        <v>1000.65</v>
+        <v>1000.42</v>
       </c>
       <c r="R4" s="14" t="n">
-        <v>999.97</v>
+        <v>999.98</v>
       </c>
       <c r="S4" s="14" t="n">
         <v>1000.01</v>
       </c>
       <c r="T4" s="14" t="n">
-        <v>1000.62</v>
+        <v>1000.53</v>
       </c>
       <c r="U4" s="14" t="n">
-        <v>999.83</v>
+        <v>999.86</v>
       </c>
       <c r="V4" s="14" t="n">
         <v>999.99</v>
       </c>
       <c r="W4" s="14" t="n">
-        <v>1000.04</v>
+        <v>1000.03</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -8468,33 +8749,15 @@
       <c r="B5" s="2" t="n">
         <v>437300</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>452603</v>
-      </c>
       <c r="D5" s="2" t="n">
         <v>926700</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>3439000</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1625800</v>
-      </c>
       <c r="G5" s="2" t="n">
         <v>5857000</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>492200</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>944800</v>
-      </c>
       <c r="J5" s="2" t="n">
         <v>335400</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>1425300</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>02/09/2026</t>
@@ -8503,33 +8766,15 @@
       <c r="N5" s="14" t="n">
         <v>1001.18</v>
       </c>
-      <c r="O5" s="14" t="n">
-        <v>1008.42</v>
-      </c>
       <c r="P5" s="14" t="n">
         <v>1002.51</v>
       </c>
-      <c r="Q5" s="14" t="n">
-        <v>1000.25</v>
-      </c>
-      <c r="R5" s="14" t="n">
-        <v>801.49</v>
-      </c>
       <c r="S5" s="14" t="n">
         <v>1000.04</v>
       </c>
-      <c r="T5" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U5" s="14" t="n">
-        <v>1000.4</v>
-      </c>
       <c r="V5" s="14" t="n">
         <v>1000.84</v>
       </c>
-      <c r="W5" s="14" t="n">
-        <v>1000.17</v>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>02/09/2026</t>
@@ -8625,6 +8870,174 @@
       </c>
       <c r="BD5" s="14" t="n">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>437010</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>557201</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>928884</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5347736</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3228466</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5857103</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>573079</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1124683</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>335130</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1856332</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>1000.52</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>1013.42</v>
+      </c>
+      <c r="P6" s="14" t="n">
+        <v>1004.87</v>
+      </c>
+      <c r="Q6" s="14" t="n">
+        <v>1001.8</v>
+      </c>
+      <c r="R6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S6" s="14" t="n">
+        <v>1000.05</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <v>1001.54</v>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>1000.24</v>
+      </c>
+      <c r="V6" s="14" t="n">
+        <v>1000.04</v>
+      </c>
+      <c r="W6" s="14" t="n">
+        <v>1000.69</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="Z6" s="14" t="n">
+        <v>1001.19</v>
+      </c>
+      <c r="AA6" s="14" t="n">
+        <v>1035.95</v>
+      </c>
+      <c r="AB6" s="14" t="n">
+        <v>1000.87</v>
+      </c>
+      <c r="AC6" s="14" t="n">
+        <v>1011.45</v>
+      </c>
+      <c r="AD6" s="14" t="n">
+        <v>999.86</v>
+      </c>
+      <c r="AE6" s="14" t="n">
+        <v>1000.42</v>
+      </c>
+      <c r="AF6" s="14" t="n">
+        <v>1002.47</v>
+      </c>
+      <c r="AG6" s="14" t="n">
+        <v>1000.57</v>
+      </c>
+      <c r="AH6" s="14" t="n">
+        <v>1000.39</v>
+      </c>
+      <c r="AI6" s="14" t="n">
+        <v>1001.29</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="AL6" s="14" t="n">
+        <v>1000.47</v>
+      </c>
+      <c r="AM6" s="14" t="n">
+        <v>1001.56</v>
+      </c>
+      <c r="AN6" s="14" t="n">
+        <v>1000.35</v>
+      </c>
+      <c r="AO6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" s="14" t="n">
+        <v>1000.32</v>
+      </c>
+      <c r="AQ6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS6" s="14" t="n">
+        <v>999.6799999999999</v>
+      </c>
+      <c r="AT6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="AX6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY6" s="14" t="n">
+        <v>1010.93</v>
+      </c>
+      <c r="AZ6" s="14" t="n">
+        <v>1000.59</v>
+      </c>
+      <c r="BA6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BB6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC6" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BD6" s="14" t="n">
+        <v>1004.71</v>
       </c>
     </row>
   </sheetData>

--- a/suivi_reseaux_politiques.xlsx
+++ b/suivi_reseaux_politiques.xlsx
@@ -13,7 +13,7 @@
     <sheet name="_donnees_graphiques" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DONNEES'!$A$1:$H$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DONNEES'!$A$1:$H$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,12 +431,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$B$3:$B$6</f>
+              <f>'_donnees_graphiques'!$B$3:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -467,12 +467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$C$3:$C$6</f>
+              <f>'_donnees_graphiques'!$C$3:$C$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -503,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$D$3:$D$6</f>
+              <f>'_donnees_graphiques'!$D$3:$D$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -539,12 +539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$E$3:$E$6</f>
+              <f>'_donnees_graphiques'!$E$3:$E$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -575,12 +575,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$F$3:$F$6</f>
+              <f>'_donnees_graphiques'!$F$3:$F$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -611,12 +611,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$G$3:$G$6</f>
+              <f>'_donnees_graphiques'!$G$3:$G$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -647,12 +647,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$6</f>
+              <f>'_donnees_graphiques'!$H$3:$H$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -683,12 +683,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$I$3:$I$6</f>
+              <f>'_donnees_graphiques'!$I$3:$I$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -719,12 +719,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$J$3:$J$6</f>
+              <f>'_donnees_graphiques'!$J$3:$J$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -755,12 +755,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$6</f>
+              <f>'_donnees_graphiques'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$K$3:$K$6</f>
+              <f>'_donnees_graphiques'!$K$3:$K$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -878,12 +878,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$N$3:$N$6</f>
+              <f>'_donnees_graphiques'!$N$3:$N$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -914,12 +914,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$O$3:$O$6</f>
+              <f>'_donnees_graphiques'!$O$3:$O$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -950,12 +950,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$P$3:$P$6</f>
+              <f>'_donnees_graphiques'!$P$3:$P$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -986,12 +986,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$Q$3:$Q$6</f>
+              <f>'_donnees_graphiques'!$Q$3:$Q$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$R$3:$R$6</f>
+              <f>'_donnees_graphiques'!$R$3:$R$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1058,12 +1058,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$S$3:$S$6</f>
+              <f>'_donnees_graphiques'!$S$3:$S$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$T$3:$T$6</f>
+              <f>'_donnees_graphiques'!$T$3:$T$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1130,12 +1130,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$U$3:$U$6</f>
+              <f>'_donnees_graphiques'!$U$3:$U$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1166,12 +1166,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$V$3:$V$6</f>
+              <f>'_donnees_graphiques'!$V$3:$V$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1202,12 +1202,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$6</f>
+              <f>'_donnees_graphiques'!$M$3:$M$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$W$3:$W$6</f>
+              <f>'_donnees_graphiques'!$W$3:$W$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1325,12 +1325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$Z$3:$Z$6</f>
+              <f>'_donnees_graphiques'!$Z$3:$Z$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1361,12 +1361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AA$3:$AA$6</f>
+              <f>'_donnees_graphiques'!$AA$3:$AA$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1397,12 +1397,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AB$3:$AB$6</f>
+              <f>'_donnees_graphiques'!$AB$3:$AB$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1433,12 +1433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AC$3:$AC$6</f>
+              <f>'_donnees_graphiques'!$AC$3:$AC$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1469,12 +1469,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AD$3:$AD$6</f>
+              <f>'_donnees_graphiques'!$AD$3:$AD$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1505,12 +1505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AE$3:$AE$6</f>
+              <f>'_donnees_graphiques'!$AE$3:$AE$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1541,12 +1541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AF$3:$AF$6</f>
+              <f>'_donnees_graphiques'!$AF$3:$AF$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1577,12 +1577,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AG$3:$AG$6</f>
+              <f>'_donnees_graphiques'!$AG$3:$AG$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1613,12 +1613,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AH$3:$AH$6</f>
+              <f>'_donnees_graphiques'!$AH$3:$AH$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1649,12 +1649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$6</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AI$3:$AI$6</f>
+              <f>'_donnees_graphiques'!$AI$3:$AI$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1772,12 +1772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AL$3:$AL$6</f>
+              <f>'_donnees_graphiques'!$AL$3:$AL$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1808,12 +1808,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AM$3:$AM$6</f>
+              <f>'_donnees_graphiques'!$AM$3:$AM$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1844,12 +1844,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AN$3:$AN$6</f>
+              <f>'_donnees_graphiques'!$AN$3:$AN$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1880,12 +1880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AO$3:$AO$6</f>
+              <f>'_donnees_graphiques'!$AO$3:$AO$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1916,12 +1916,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AP$3:$AP$6</f>
+              <f>'_donnees_graphiques'!$AP$3:$AP$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1952,12 +1952,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AQ$3:$AQ$6</f>
+              <f>'_donnees_graphiques'!$AQ$3:$AQ$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1988,12 +1988,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AR$3:$AR$6</f>
+              <f>'_donnees_graphiques'!$AR$3:$AR$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AS$3:$AS$6</f>
+              <f>'_donnees_graphiques'!$AS$3:$AS$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AT$3:$AT$6</f>
+              <f>'_donnees_graphiques'!$AT$3:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2096,12 +2096,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$6</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AU$3:$AU$6</f>
+              <f>'_donnees_graphiques'!$AU$3:$AU$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2219,12 +2219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AX$3:$AX$6</f>
+              <f>'_donnees_graphiques'!$AX$3:$AX$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2255,12 +2255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AY$3:$AY$6</f>
+              <f>'_donnees_graphiques'!$AY$3:$AY$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2291,12 +2291,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AZ$3:$AZ$6</f>
+              <f>'_donnees_graphiques'!$AZ$3:$AZ$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2327,12 +2327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BA$3:$BA$6</f>
+              <f>'_donnees_graphiques'!$BA$3:$BA$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2363,12 +2363,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BB$3:$BB$6</f>
+              <f>'_donnees_graphiques'!$BB$3:$BB$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2399,12 +2399,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BC$3:$BC$6</f>
+              <f>'_donnees_graphiques'!$BC$3:$BC$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BD$3:$BD$6</f>
+              <f>'_donnees_graphiques'!$BD$3:$BD$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2471,12 +2471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BE$3:$BE$6</f>
+              <f>'_donnees_graphiques'!$BE$3:$BE$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2507,12 +2507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BF$3:$BF$6</f>
+              <f>'_donnees_graphiques'!$BF$3:$BF$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2543,12 +2543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$6</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BG$3:$BG$6</f>
+              <f>'_donnees_graphiques'!$BG$3:$BG$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3023,7 +3023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4162,8 +4162,294 @@
         <v>658479</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>192200</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>102000</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>18700</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>576900</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>213300</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>69000</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>84900</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <v>591200</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>218225</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>941200</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>266000</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>431000</v>
+      </c>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="19" t="n">
+        <v>1856425</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="n">
+        <v>462128</v>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>286700</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>487000</v>
+      </c>
+      <c r="G45" s="22" t="n">
+        <v>682100</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>2097928</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>30700</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>205400</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="18" t="n"/>
+      <c r="H46" s="19" t="n">
+        <v>335100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n">
+        <v>757258</v>
+      </c>
+      <c r="D47" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>7357258</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>1402635</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>626000</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>5628635</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="n">
+        <v>847000</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="F49" s="22" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G49" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H49" s="23" t="n">
+        <v>8385000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>637000</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>307800</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="19" t="n">
+        <v>1124800</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="n">
+        <v>356973</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>136200</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F51" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G51" s="22" t="n">
+        <v>85500</v>
+      </c>
+      <c r="H51" s="23" t="n">
+        <v>698673</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H41"/>
+  <autoFilter ref="A1:H51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4175,7 +4461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4201,7 +4487,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Dernier releve : 03/09/2026   -   10 personnalites suivies</t>
+          <t>Dernier releve : 04/09/2026   -   10 personnalites suivies</t>
         </is>
       </c>
     </row>
@@ -4289,10 +4575,10 @@
         </is>
       </c>
       <c r="B7" s="31" t="n">
-        <v>8347736</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>8736</v>
+        <v>8385000</v>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>-736</v>
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
@@ -4315,10 +4601,10 @@
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>9595</v>
+        <v>8859</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>0.1797442218180345</v>
+        <v>0.165956650451915</v>
       </c>
     </row>
     <row r="8">
@@ -4328,10 +4614,10 @@
         </is>
       </c>
       <c r="B8" s="36" t="n">
-        <v>7357103</v>
+        <v>7357258</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
@@ -4354,10 +4640,10 @@
         </is>
       </c>
       <c r="H8" s="37" t="n">
-        <v>317</v>
+        <v>472</v>
       </c>
       <c r="I8" s="39" t="n">
-        <v>0.005412524889925052</v>
+        <v>0.008059027596374335</v>
       </c>
     </row>
     <row r="9">
@@ -4367,10 +4653,10 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>5628466</v>
+        <v>5628635</v>
       </c>
       <c r="C9" s="32" t="n">
-        <v>402666</v>
+        <v>169</v>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
@@ -4392,24 +4678,24 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="H9" s="40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I9" s="41" t="n">
-        <v>-3.097445320232595e-05</v>
+      <c r="H9" s="32" t="n">
+        <v>168</v>
+      </c>
+      <c r="I9" s="34" t="n">
+        <v>0.005203708137635488</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>Édouard Philippe</t>
+          <t>Gabriel Attal</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
-        <v>1856332</v>
-      </c>
-      <c r="C10" s="37" t="n">
-        <v>32</v>
+        <v>2097928</v>
+      </c>
+      <c r="C10" s="42" t="n">
+        <v>-56</v>
       </c>
       <c r="D10" s="38" t="inlineStr">
         <is>
@@ -4432,23 +4718,23 @@
         </is>
       </c>
       <c r="H10" s="37" t="n">
-        <v>1281</v>
+        <v>4446</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.06905470523452806</v>
+        <v>0.3150103940676496</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Gabriel Attal</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>1610984</v>
+        <v>1856425</v>
       </c>
       <c r="C11" s="32" t="n">
-        <v>2584</v>
+        <v>93</v>
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
@@ -4471,10 +4757,10 @@
         </is>
       </c>
       <c r="H11" s="32" t="n">
-        <v>4502</v>
+        <v>1374</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>0.4870280901185797</v>
+        <v>0.07406804449041626</v>
       </c>
     </row>
     <row r="12">
@@ -4484,10 +4770,10 @@
         </is>
       </c>
       <c r="B12" s="36" t="n">
-        <v>1522683</v>
-      </c>
-      <c r="C12" s="42" t="n">
-        <v>-117</v>
+        <v>1124800</v>
+      </c>
+      <c r="C12" s="37" t="n">
+        <v>117</v>
       </c>
       <c r="D12" s="38" t="inlineStr">
         <is>
@@ -4510,10 +4796,10 @@
         </is>
       </c>
       <c r="H12" s="37" t="n">
-        <v>265</v>
+        <v>382</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>0.02356774793714767</v>
+        <v>0.03397313098865151</v>
       </c>
     </row>
     <row r="13">
@@ -4523,10 +4809,10 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>658479</v>
+        <v>698673</v>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1279</v>
+        <v>194</v>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
@@ -4549,23 +4835,23 @@
         </is>
       </c>
       <c r="H13" s="32" t="n">
-        <v>879</v>
+        <v>973</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>0.1536176162181047</v>
+        <v>0.1700454386578176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>David Lisnard</t>
+          <t>Bruno Retailleau</t>
         </is>
       </c>
       <c r="B14" s="36" t="n">
-        <v>575701</v>
+        <v>591200</v>
       </c>
       <c r="C14" s="37" t="n">
-        <v>3798</v>
+        <v>290</v>
       </c>
       <c r="D14" s="38" t="inlineStr">
         <is>
@@ -4588,23 +4874,23 @@
         </is>
       </c>
       <c r="H14" s="37" t="n">
-        <v>7376</v>
+        <v>516</v>
       </c>
       <c r="I14" s="39" t="n">
-        <v>1.341517755649524</v>
+        <v>0.1020198345538903</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Bruno Retailleau</t>
+          <t>David Lisnard</t>
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>521910</v>
-      </c>
-      <c r="C15" s="40" t="n">
-        <v>-290</v>
+        <v>576900</v>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>1199</v>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
@@ -4627,10 +4913,10 @@
         </is>
       </c>
       <c r="H15" s="32" t="n">
-        <v>226</v>
+        <v>8375</v>
       </c>
       <c r="I15" s="34" t="n">
-        <v>0.05174182204477074</v>
+        <v>1.523211931068968</v>
       </c>
     </row>
     <row r="16">
@@ -4640,10 +4926,10 @@
         </is>
       </c>
       <c r="B16" s="36" t="n">
-        <v>335130</v>
+        <v>335100</v>
       </c>
       <c r="C16" s="42" t="n">
-        <v>-270</v>
+        <v>-30</v>
       </c>
       <c r="D16" s="38" t="inlineStr">
         <is>
@@ -4665,11 +4951,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="H16" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" s="39" t="n">
-        <v>0.003580828245564049</v>
+      <c r="H16" s="42" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>-0.005371242368357176</v>
       </c>
     </row>
     <row r="18">
@@ -4736,7 +5022,7 @@
         </is>
       </c>
       <c r="B22" s="46" t="n">
-        <v>105710</v>
+        <v>106000</v>
       </c>
       <c r="C22" s="46" t="n">
         <v>213300</v>
@@ -4751,7 +5037,7 @@
         <v>84900</v>
       </c>
       <c r="G22" s="47" t="n">
-        <v>521910</v>
+        <v>591200</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -4761,22 +5047,22 @@
         </is>
       </c>
       <c r="B23" s="49" t="n">
-        <v>175101</v>
+        <v>175000</v>
       </c>
       <c r="C23" s="49" t="n">
-        <v>192100</v>
+        <v>192200</v>
       </c>
       <c r="D23" s="49" t="n">
         <v>89000</v>
       </c>
       <c r="E23" s="49" t="n">
-        <v>101000</v>
+        <v>102000</v>
       </c>
       <c r="F23" s="49" t="n">
-        <v>18500</v>
+        <v>18700</v>
       </c>
       <c r="G23" s="50" t="n">
-        <v>575701</v>
+        <v>576900</v>
       </c>
     </row>
     <row r="24">
@@ -4786,7 +5072,7 @@
         </is>
       </c>
       <c r="B24" s="46" t="n">
-        <v>462184</v>
+        <v>462128</v>
       </c>
       <c r="C24" s="46" t="n">
         <v>286700</v>
@@ -4801,7 +5087,7 @@
         <v>682100</v>
       </c>
       <c r="G24" s="47" t="n">
-        <v>1610984</v>
+        <v>2097928</v>
       </c>
     </row>
     <row r="25">
@@ -4811,7 +5097,7 @@
         </is>
       </c>
       <c r="B25" s="49" t="n">
-        <v>847736</v>
+        <v>847000</v>
       </c>
       <c r="C25" s="49" t="n">
         <v>2600000</v>
@@ -4819,16 +5105,14 @@
       <c r="D25" s="49" t="n">
         <v>1900000</v>
       </c>
-      <c r="E25" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E25" s="49" t="n">
+        <v>38000</v>
       </c>
       <c r="F25" s="49" t="n">
         <v>3000000</v>
       </c>
       <c r="G25" s="50" t="n">
-        <v>8347736</v>
+        <v>8385000</v>
       </c>
     </row>
     <row r="26">
@@ -4838,10 +5122,10 @@
         </is>
       </c>
       <c r="B26" s="46" t="n">
-        <v>1402566</v>
+        <v>1402635</v>
       </c>
       <c r="C26" s="46" t="n">
-        <v>625900</v>
+        <v>626000</v>
       </c>
       <c r="D26" s="46" t="n">
         <v>1200000</v>
@@ -4855,7 +5139,7 @@
         <v>2400000</v>
       </c>
       <c r="G26" s="47" t="n">
-        <v>5628466</v>
+        <v>5628635</v>
       </c>
     </row>
     <row r="27">
@@ -4865,7 +5149,7 @@
         </is>
       </c>
       <c r="B27" s="49" t="n">
-        <v>757103</v>
+        <v>757258</v>
       </c>
       <c r="C27" s="49" t="n">
         <v>3000000</v>
@@ -4882,7 +5166,7 @@
         <v>1500000</v>
       </c>
       <c r="G27" s="50" t="n">
-        <v>7357103</v>
+        <v>7357258</v>
       </c>
     </row>
     <row r="28">
@@ -4892,7 +5176,7 @@
         </is>
       </c>
       <c r="B28" s="46" t="n">
-        <v>356879</v>
+        <v>356973</v>
       </c>
       <c r="C28" s="46" t="n">
         <v>136200</v>
@@ -4900,16 +5184,14 @@
       <c r="D28" s="46" t="n">
         <v>80000</v>
       </c>
-      <c r="E28" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E28" s="46" t="n">
+        <v>40000</v>
       </c>
       <c r="F28" s="46" t="n">
-        <v>85400</v>
+        <v>85500</v>
       </c>
       <c r="G28" s="47" t="n">
-        <v>658479</v>
+        <v>698673</v>
       </c>
     </row>
     <row r="29">
@@ -4919,7 +5201,7 @@
         </is>
       </c>
       <c r="B29" s="49" t="n">
-        <v>636883</v>
+        <v>637000</v>
       </c>
       <c r="C29" s="49" t="n">
         <v>307800</v>
@@ -4936,7 +5218,7 @@
         </is>
       </c>
       <c r="G29" s="50" t="n">
-        <v>1522683</v>
+        <v>1124800</v>
       </c>
     </row>
     <row r="30">
@@ -4946,7 +5228,7 @@
         </is>
       </c>
       <c r="B30" s="46" t="n">
-        <v>30730</v>
+        <v>30700</v>
       </c>
       <c r="C30" s="46" t="n">
         <v>205400</v>
@@ -4963,7 +5245,7 @@
         </is>
       </c>
       <c r="G30" s="47" t="n">
-        <v>335130</v>
+        <v>335100</v>
       </c>
     </row>
     <row r="31">
@@ -4973,7 +5255,7 @@
         </is>
       </c>
       <c r="B31" s="49" t="n">
-        <v>218132</v>
+        <v>218225</v>
       </c>
       <c r="C31" s="49" t="n">
         <v>941200</v>
@@ -4990,7 +5272,7 @@
         </is>
       </c>
       <c r="G31" s="50" t="n">
-        <v>1856332</v>
+        <v>1856425</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -5078,13 +5360,13 @@
         </is>
       </c>
       <c r="C36" s="52" t="n">
-        <v>105710</v>
-      </c>
-      <c r="D36" s="40" t="n">
-        <v>-290</v>
-      </c>
-      <c r="E36" s="41" t="n">
-        <v>-0.2735849056603734</v>
+        <v>106000</v>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>290</v>
+      </c>
+      <c r="E36" s="34" t="n">
+        <v>0.2743354460315928</v>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
@@ -5107,10 +5389,10 @@
         </is>
       </c>
       <c r="J36" s="32" t="n">
-        <v>126</v>
+        <v>416</v>
       </c>
       <c r="K36" s="34" t="n">
-        <v>0.1193362630701689</v>
+        <v>0.3939990907713353</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -5251,15 +5533,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J39" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K39" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5325,13 +5603,13 @@
         </is>
       </c>
       <c r="C41" s="56" t="n">
-        <v>521910</v>
-      </c>
-      <c r="D41" s="59" t="n">
-        <v>-290</v>
-      </c>
-      <c r="E41" s="60" t="n">
-        <v>-0.05553427805438105</v>
+        <v>591200</v>
+      </c>
+      <c r="D41" s="57" t="n">
+        <v>290</v>
+      </c>
+      <c r="E41" s="58" t="n">
+        <v>0.05556513575137867</v>
       </c>
       <c r="F41" s="55" t="inlineStr">
         <is>
@@ -5354,10 +5632,10 @@
         </is>
       </c>
       <c r="J41" s="57" t="n">
-        <v>226</v>
+        <v>516</v>
       </c>
       <c r="K41" s="58" t="n">
-        <v>0.05174182204477074</v>
+        <v>0.1020198345538903</v>
       </c>
     </row>
     <row r="42">
@@ -5372,13 +5650,13 @@
         </is>
       </c>
       <c r="C42" s="52" t="n">
-        <v>175101</v>
-      </c>
-      <c r="D42" s="32" t="n">
-        <v>2398</v>
-      </c>
-      <c r="E42" s="34" t="n">
-        <v>1.388510911796548</v>
+        <v>175000</v>
+      </c>
+      <c r="D42" s="40" t="n">
+        <v>-101</v>
+      </c>
+      <c r="E42" s="41" t="n">
+        <v>-0.05768099553972172</v>
       </c>
       <c r="F42" s="51" t="inlineStr">
         <is>
@@ -5401,10 +5679,10 @@
         </is>
       </c>
       <c r="J42" s="32" t="n">
-        <v>6076</v>
+        <v>5975</v>
       </c>
       <c r="K42" s="34" t="n">
-        <v>3.59473450672978</v>
+        <v>3.534980032539559</v>
       </c>
     </row>
     <row r="43">
@@ -5419,13 +5697,13 @@
         </is>
       </c>
       <c r="C43" s="52" t="n">
-        <v>192100</v>
+        <v>192200</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="34" t="n">
-        <v>0.1042209484106271</v>
+        <v>0.05205622071837723</v>
       </c>
       <c r="F43" s="51" t="inlineStr">
         <is>
@@ -5448,10 +5726,10 @@
         </is>
       </c>
       <c r="J43" s="32" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K43" s="34" t="n">
-        <v>0.1564129301355521</v>
+        <v>0.2085505735140769</v>
       </c>
     </row>
     <row r="44">
@@ -5468,11 +5746,11 @@
       <c r="C44" s="52" t="n">
         <v>89000</v>
       </c>
-      <c r="D44" s="32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E44" s="34" t="n">
-        <v>1.136363636363646</v>
+      <c r="D44" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="51" t="inlineStr">
         <is>
@@ -5513,17 +5791,13 @@
         </is>
       </c>
       <c r="C45" s="52" t="n">
-        <v>101000</v>
-      </c>
-      <c r="D45" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E45" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>102000</v>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="34" t="n">
+        <v>0.990099009900991</v>
       </c>
       <c r="F45" s="51" t="inlineStr">
         <is>
@@ -5545,11 +5819,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J45" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="54" t="n">
-        <v>0</v>
+      <c r="J45" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K45" s="34" t="n">
+        <v>0.990099009900991</v>
       </c>
     </row>
     <row r="46">
@@ -5564,13 +5838,13 @@
         </is>
       </c>
       <c r="C46" s="52" t="n">
-        <v>18500</v>
+        <v>18700</v>
       </c>
       <c r="D46" s="32" t="n">
         <v>200</v>
       </c>
       <c r="E46" s="34" t="n">
-        <v>1.092896174863389</v>
+        <v>1.08108108108107</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
@@ -5615,13 +5889,13 @@
         </is>
       </c>
       <c r="C47" s="56" t="n">
-        <v>575701</v>
+        <v>576900</v>
       </c>
       <c r="D47" s="57" t="n">
-        <v>3798</v>
+        <v>1199</v>
       </c>
       <c r="E47" s="58" t="n">
-        <v>0.8065355285483466</v>
+        <v>0.2082678334760502</v>
       </c>
       <c r="F47" s="55" t="inlineStr">
         <is>
@@ -5644,10 +5918,10 @@
         </is>
       </c>
       <c r="J47" s="57" t="n">
-        <v>7376</v>
+        <v>8375</v>
       </c>
       <c r="K47" s="58" t="n">
-        <v>1.341517755649524</v>
+        <v>1.523211931068968</v>
       </c>
     </row>
     <row r="48">
@@ -5662,13 +5936,13 @@
         </is>
       </c>
       <c r="C48" s="52" t="n">
-        <v>462184</v>
-      </c>
-      <c r="D48" s="32" t="n">
-        <v>184</v>
-      </c>
-      <c r="E48" s="34" t="n">
-        <v>0.03982683982683977</v>
+        <v>462128</v>
+      </c>
+      <c r="D48" s="40" t="n">
+        <v>-56</v>
+      </c>
+      <c r="E48" s="41" t="n">
+        <v>-0.01211638654734504</v>
       </c>
       <c r="F48" s="51" t="inlineStr">
         <is>
@@ -5691,10 +5965,10 @@
         </is>
       </c>
       <c r="J48" s="32" t="n">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="K48" s="34" t="n">
-        <v>0.08705406447198083</v>
+        <v>0.0749271301176746</v>
       </c>
     </row>
     <row r="49">
@@ -5758,11 +6032,11 @@
       <c r="C50" s="52" t="n">
         <v>180000</v>
       </c>
-      <c r="D50" s="32" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E50" s="34" t="n">
-        <v>1.12359550561798</v>
+      <c r="D50" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
@@ -5835,15 +6109,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J51" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K51" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J51" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -5860,11 +6130,11 @@
       <c r="C52" s="52" t="n">
         <v>682100</v>
       </c>
-      <c r="D52" s="32" t="n">
-        <v>400</v>
-      </c>
-      <c r="E52" s="34" t="n">
-        <v>0.05867683731846096</v>
+      <c r="D52" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
@@ -5909,13 +6179,13 @@
         </is>
       </c>
       <c r="C53" s="56" t="n">
-        <v>1610984</v>
-      </c>
-      <c r="D53" s="57" t="n">
-        <v>2584</v>
-      </c>
-      <c r="E53" s="58" t="n">
-        <v>0.16065655309625</v>
+        <v>2097928</v>
+      </c>
+      <c r="D53" s="59" t="n">
+        <v>-56</v>
+      </c>
+      <c r="E53" s="60" t="n">
+        <v>-0.003476136324132018</v>
       </c>
       <c r="F53" s="55" t="inlineStr">
         <is>
@@ -5938,10 +6208,10 @@
         </is>
       </c>
       <c r="J53" s="57" t="n">
-        <v>4502</v>
+        <v>4446</v>
       </c>
       <c r="K53" s="58" t="n">
-        <v>0.4870280901185797</v>
+        <v>0.3150103940676496</v>
       </c>
     </row>
     <row r="54">
@@ -5956,13 +6226,13 @@
         </is>
       </c>
       <c r="C54" s="52" t="n">
-        <v>847736</v>
-      </c>
-      <c r="D54" s="32" t="n">
-        <v>8736</v>
-      </c>
-      <c r="E54" s="34" t="n">
-        <v>1.041239570917751</v>
+        <v>847000</v>
+      </c>
+      <c r="D54" s="40" t="n">
+        <v>-736</v>
+      </c>
+      <c r="E54" s="41" t="n">
+        <v>-0.08681948153670405</v>
       </c>
       <c r="F54" s="51" t="inlineStr">
         <is>
@@ -5985,10 +6255,10 @@
         </is>
       </c>
       <c r="J54" s="32" t="n">
-        <v>9595</v>
+        <v>8859</v>
       </c>
       <c r="K54" s="34" t="n">
-        <v>1.144795446112279</v>
+        <v>1.056982059104605</v>
       </c>
     </row>
     <row r="55">
@@ -6052,15 +6322,11 @@
       <c r="C56" s="52" t="n">
         <v>1900000</v>
       </c>
-      <c r="D56" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E56" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D56" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
@@ -6097,141 +6363,149 @@
       </c>
       <c r="B57" s="51" t="inlineStr">
         <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="C57" s="52" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K57" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="51" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="B58" s="51" t="inlineStr">
+        <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C57" s="52" t="n">
+      <c r="C58" s="52" t="n">
         <v>3000000</v>
       </c>
-      <c r="D57" s="53" t="n">
+      <c r="D58" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="54" t="n">
+      <c r="E58" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K57" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+      <c r="F58" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G58" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H58" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I58" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J58" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K58" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="55" t="inlineStr">
         <is>
           <t>Jean-Luc Mélenchon</t>
         </is>
       </c>
-      <c r="B58" s="55" t="inlineStr">
+      <c r="B59" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C58" s="56" t="n">
-        <v>8347736</v>
-      </c>
-      <c r="D58" s="57" t="n">
-        <v>8736</v>
-      </c>
-      <c r="E58" s="58" t="n">
-        <v>0.1356732411865291</v>
-      </c>
-      <c r="F58" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G58" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H58" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I58" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J58" s="57" t="n">
-        <v>9595</v>
-      </c>
-      <c r="K58" s="58" t="n">
-        <v>0.1797442218180345</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="51" t="inlineStr">
-        <is>
-          <t>Jordan Bardella</t>
-        </is>
-      </c>
-      <c r="B59" s="51" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C59" s="52" t="n">
-        <v>1402566</v>
-      </c>
-      <c r="D59" s="32" t="n">
-        <v>402566</v>
-      </c>
-      <c r="E59" s="34" t="n">
-        <v>40.2566</v>
-      </c>
-      <c r="F59" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G59" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H59" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I59" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J59" s="40" t="n">
-        <v>-201</v>
-      </c>
-      <c r="K59" s="41" t="n">
-        <v>-0.01432882296205085</v>
+      <c r="C59" s="56" t="n">
+        <v>8385000</v>
+      </c>
+      <c r="D59" s="59" t="n">
+        <v>-736</v>
+      </c>
+      <c r="E59" s="60" t="n">
+        <v>-0.008816761814223195</v>
+      </c>
+      <c r="F59" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G59" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H59" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I59" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J59" s="57" t="n">
+        <v>8859</v>
+      </c>
+      <c r="K59" s="58" t="n">
+        <v>0.165956650451915</v>
       </c>
     </row>
     <row r="60">
@@ -6242,17 +6516,17 @@
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C60" s="52" t="n">
-        <v>625900</v>
+        <v>1402635</v>
       </c>
       <c r="D60" s="32" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E60" s="34" t="n">
-        <v>0.0159795461808887</v>
+        <v>0.004919554587812236</v>
       </c>
       <c r="F60" s="51" t="inlineStr">
         <is>
@@ -6274,11 +6548,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J60" s="32" t="n">
-        <v>200</v>
-      </c>
-      <c r="K60" s="34" t="n">
-        <v>0.03196420009590195</v>
+      <c r="J60" s="40" t="n">
+        <v>-132</v>
+      </c>
+      <c r="K60" s="41" t="n">
+        <v>-0.00940997328851001</v>
       </c>
     </row>
     <row r="61">
@@ -6289,21 +6563,17 @@
       </c>
       <c r="B61" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C61" s="52" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D61" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E61" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>626000</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" s="34" t="n">
+        <v>0.01597699312989587</v>
       </c>
       <c r="F61" s="51" t="inlineStr">
         <is>
@@ -6325,11 +6595,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J61" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="54" t="n">
-        <v>0</v>
+      <c r="J61" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="K61" s="34" t="n">
+        <v>0.04794630014384182</v>
       </c>
     </row>
     <row r="62">
@@ -6340,11 +6610,11 @@
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C62" s="52" t="n">
-        <v>2400000</v>
+        <v>1200000</v>
       </c>
       <c r="D62" s="53" t="n">
         <v>0</v>
@@ -6372,109 +6642,109 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J62" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K62" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J62" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="inlineStr">
+      <c r="A63" s="51" t="inlineStr">
         <is>
           <t>Jordan Bardella</t>
         </is>
       </c>
-      <c r="B63" s="55" t="inlineStr">
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C63" s="52" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="D63" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G63" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H63" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I63" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J63" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K63" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="B64" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C63" s="56" t="n">
-        <v>5628466</v>
-      </c>
-      <c r="D63" s="57" t="n">
-        <v>402666</v>
-      </c>
-      <c r="E63" s="58" t="n">
-        <v>10.00213622137216</v>
-      </c>
-      <c r="F63" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G63" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H63" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I63" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J63" s="59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K63" s="60" t="n">
-        <v>-3.097445320232595e-05</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="51" t="inlineStr">
-        <is>
-          <t>Marine Le Pen</t>
-        </is>
-      </c>
-      <c r="B64" s="51" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C64" s="52" t="n">
-        <v>757103</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>103</v>
-      </c>
-      <c r="E64" s="34" t="n">
-        <v>0.01360634081901679</v>
-      </c>
-      <c r="F64" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G64" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H64" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I64" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J64" s="32" t="n">
-        <v>317</v>
-      </c>
-      <c r="K64" s="34" t="n">
-        <v>0.04188766705515157</v>
+      <c r="C64" s="56" t="n">
+        <v>5628635</v>
+      </c>
+      <c r="D64" s="57" t="n">
+        <v>169</v>
+      </c>
+      <c r="E64" s="58" t="n">
+        <v>0.003002594312562223</v>
+      </c>
+      <c r="F64" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G64" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H64" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I64" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J64" s="57" t="n">
+        <v>168</v>
+      </c>
+      <c r="K64" s="58" t="n">
+        <v>0.005203708137635488</v>
       </c>
     </row>
     <row r="65">
@@ -6485,17 +6755,17 @@
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C65" s="52" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D65" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="54" t="n">
-        <v>0</v>
+        <v>757258</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>155</v>
+      </c>
+      <c r="E65" s="34" t="n">
+        <v>0.02047277583103746</v>
       </c>
       <c r="F65" s="51" t="inlineStr">
         <is>
@@ -6517,11 +6787,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J65" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="54" t="n">
-        <v>0</v>
+      <c r="J65" s="32" t="n">
+        <v>472</v>
+      </c>
+      <c r="K65" s="34" t="n">
+        <v>0.06236901845435572</v>
       </c>
     </row>
     <row r="66">
@@ -6532,11 +6802,11 @@
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C66" s="52" t="n">
-        <v>2100000</v>
+        <v>3000000</v>
       </c>
       <c r="D66" s="53" t="n">
         <v>0</v>
@@ -6579,11 +6849,11 @@
       </c>
       <c r="B67" s="51" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C67" s="52" t="n">
-        <v>1500000</v>
+        <v>2100000</v>
       </c>
       <c r="D67" s="53" t="n">
         <v>0</v>
@@ -6611,109 +6881,109 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J67" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K67" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J67" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="55" t="inlineStr">
+      <c r="A68" s="51" t="inlineStr">
         <is>
           <t>Marine Le Pen</t>
         </is>
       </c>
-      <c r="B68" s="55" t="inlineStr">
+      <c r="B68" s="51" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C68" s="52" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D68" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G68" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H68" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I68" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J68" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K68" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="55" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C68" s="56" t="n">
-        <v>7357103</v>
-      </c>
-      <c r="D68" s="57" t="n">
-        <v>103</v>
-      </c>
-      <c r="E68" s="58" t="n">
-        <v>0.001400027184983443</v>
-      </c>
-      <c r="F68" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G68" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H68" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I68" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J68" s="57" t="n">
-        <v>317</v>
-      </c>
-      <c r="K68" s="58" t="n">
-        <v>0.005412524889925052</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="51" t="inlineStr">
-        <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
-      <c r="B69" s="51" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C69" s="52" t="n">
-        <v>356879</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>879</v>
-      </c>
-      <c r="E69" s="34" t="n">
-        <v>0.2469101123595552</v>
-      </c>
-      <c r="F69" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G69" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H69" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I69" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J69" s="32" t="n">
-        <v>879</v>
-      </c>
-      <c r="K69" s="34" t="n">
-        <v>0.2469101123595552</v>
+      <c r="C69" s="56" t="n">
+        <v>7357258</v>
+      </c>
+      <c r="D69" s="57" t="n">
+        <v>155</v>
+      </c>
+      <c r="E69" s="58" t="n">
+        <v>0.002106807530077859</v>
+      </c>
+      <c r="F69" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G69" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H69" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I69" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J69" s="57" t="n">
+        <v>472</v>
+      </c>
+      <c r="K69" s="58" t="n">
+        <v>0.008059027596374335</v>
       </c>
     </row>
     <row r="70">
@@ -6724,17 +6994,17 @@
       </c>
       <c r="B70" s="51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C70" s="52" t="n">
-        <v>136200</v>
-      </c>
-      <c r="D70" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="54" t="n">
-        <v>0</v>
+        <v>356973</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>94</v>
+      </c>
+      <c r="E70" s="34" t="n">
+        <v>0.02633945959273909</v>
       </c>
       <c r="F70" s="51" t="inlineStr">
         <is>
@@ -6756,11 +7026,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J70" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="54" t="n">
-        <v>0</v>
+      <c r="J70" s="32" t="n">
+        <v>973</v>
+      </c>
+      <c r="K70" s="34" t="n">
+        <v>0.2733146067415815</v>
       </c>
     </row>
     <row r="71">
@@ -6771,21 +7041,17 @@
       </c>
       <c r="B71" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C71" s="52" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D71" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E71" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>136200</v>
+      </c>
+      <c r="D71" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="51" t="inlineStr">
         <is>
@@ -6822,17 +7088,17 @@
       </c>
       <c r="B72" s="51" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C72" s="52" t="n">
-        <v>85400</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>400</v>
-      </c>
-      <c r="E72" s="34" t="n">
-        <v>0.4705882352941115</v>
+        <v>80000</v>
+      </c>
+      <c r="D72" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
@@ -6854,83 +7120,87 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J72" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K72" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J72" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="55" t="inlineStr">
+      <c r="A73" s="51" t="inlineStr">
         <is>
           <t>Marine Tondelier</t>
         </is>
       </c>
-      <c r="B73" s="55" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C73" s="56" t="n">
-        <v>658479</v>
-      </c>
-      <c r="D73" s="57" t="n">
-        <v>1279</v>
-      </c>
-      <c r="E73" s="58" t="n">
-        <v>0.2215869715869623</v>
-      </c>
-      <c r="F73" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G73" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H73" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I73" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J73" s="57" t="n">
-        <v>879</v>
-      </c>
-      <c r="K73" s="58" t="n">
-        <v>0.1536176162181047</v>
+      <c r="B73" s="51" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="C73" s="52" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K73" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="51" t="inlineStr">
         <is>
-          <t>Raphaël Glucksmann</t>
+          <t>Marine Tondelier</t>
         </is>
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C74" s="52" t="n">
-        <v>636883</v>
-      </c>
-      <c r="D74" s="40" t="n">
-        <v>-117</v>
-      </c>
-      <c r="E74" s="41" t="n">
-        <v>-0.01836734693877462</v>
+        <v>85500</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" s="34" t="n">
+        <v>0.117096018735352</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
@@ -6952,58 +7222,62 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J74" s="32" t="n">
-        <v>365</v>
-      </c>
-      <c r="K74" s="34" t="n">
-        <v>0.05734323302719613</v>
+      <c r="J74" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K74" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="51" t="inlineStr">
-        <is>
-          <t>Raphaël Glucksmann</t>
-        </is>
-      </c>
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C75" s="52" t="n">
-        <v>307800</v>
-      </c>
-      <c r="D75" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G75" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H75" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I75" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J75" s="40" t="n">
-        <v>-100</v>
-      </c>
-      <c r="K75" s="41" t="n">
-        <v>-0.03247807729782615</v>
+      <c r="A75" s="55" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="B75" s="55" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C75" s="56" t="n">
+        <v>698673</v>
+      </c>
+      <c r="D75" s="57" t="n">
+        <v>194</v>
+      </c>
+      <c r="E75" s="58" t="n">
+        <v>0.02946183553309556</v>
+      </c>
+      <c r="F75" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G75" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H75" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I75" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J75" s="57" t="n">
+        <v>973</v>
+      </c>
+      <c r="K75" s="58" t="n">
+        <v>0.1700454386578176</v>
       </c>
     </row>
     <row r="76">
@@ -7014,21 +7288,17 @@
       </c>
       <c r="B76" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C76" s="52" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D76" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E76" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>637000</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>117</v>
+      </c>
+      <c r="E76" s="34" t="n">
+        <v>0.01837072115287164</v>
       </c>
       <c r="F76" s="51" t="inlineStr">
         <is>
@@ -7050,11 +7320,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J76" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="54" t="n">
-        <v>0</v>
+      <c r="J76" s="32" t="n">
+        <v>482</v>
+      </c>
+      <c r="K76" s="34" t="n">
+        <v>0.07572448854549219</v>
       </c>
     </row>
     <row r="77">
@@ -7065,21 +7335,17 @@
       </c>
       <c r="B77" s="51" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C77" s="52" t="n">
-        <v>398000</v>
-      </c>
-      <c r="D77" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E77" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>307800</v>
+      </c>
+      <c r="D77" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="51" t="inlineStr">
         <is>
@@ -7101,83 +7367,83 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J77" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K77" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J77" s="40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="K77" s="41" t="n">
+        <v>-0.03247807729782615</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="55" t="inlineStr">
+      <c r="A78" s="51" t="inlineStr">
         <is>
           <t>Raphaël Glucksmann</t>
         </is>
       </c>
-      <c r="B78" s="55" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C78" s="56" t="n">
-        <v>1522683</v>
-      </c>
-      <c r="D78" s="59" t="n">
-        <v>-117</v>
-      </c>
-      <c r="E78" s="60" t="n">
-        <v>-0.01238357324301331</v>
-      </c>
-      <c r="F78" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G78" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H78" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I78" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J78" s="57" t="n">
-        <v>265</v>
-      </c>
-      <c r="K78" s="58" t="n">
-        <v>0.02356774793714767</v>
+      <c r="B78" s="51" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C78" s="52" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D78" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G78" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H78" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I78" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J78" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="51" t="inlineStr">
         <is>
-          <t>Xavier Bertrand</t>
+          <t>Raphaël Glucksmann</t>
         </is>
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="C79" s="52" t="n">
-        <v>30730</v>
-      </c>
-      <c r="D79" s="40" t="n">
-        <v>-270</v>
-      </c>
-      <c r="E79" s="41" t="n">
-        <v>-0.87096774193548</v>
+        <v>398000</v>
+      </c>
+      <c r="D79" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E79" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="F79" s="51" t="inlineStr">
         <is>
@@ -7199,58 +7465,62 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J79" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>0.03906504329709293</v>
+      <c r="J79" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K79" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="51" t="inlineStr">
-        <is>
-          <t>Xavier Bertrand</t>
-        </is>
-      </c>
-      <c r="B80" s="51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C80" s="52" t="n">
-        <v>205400</v>
-      </c>
-      <c r="D80" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G80" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H80" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I80" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J80" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="54" t="n">
-        <v>0</v>
+      <c r="A80" s="55" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="B80" s="55" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C80" s="56" t="n">
+        <v>1124800</v>
+      </c>
+      <c r="D80" s="57" t="n">
+        <v>117</v>
+      </c>
+      <c r="E80" s="58" t="n">
+        <v>0.01040293131486791</v>
+      </c>
+      <c r="F80" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G80" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H80" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I80" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J80" s="57" t="n">
+        <v>382</v>
+      </c>
+      <c r="K80" s="58" t="n">
+        <v>0.03397313098865151</v>
       </c>
     </row>
     <row r="81">
@@ -7261,17 +7531,17 @@
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C81" s="52" t="n">
-        <v>99000</v>
-      </c>
-      <c r="D81" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="54" t="n">
-        <v>0</v>
+        <v>30700</v>
+      </c>
+      <c r="D81" s="40" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E81" s="41" t="n">
+        <v>-0.09762447120078566</v>
       </c>
       <c r="F81" s="51" t="inlineStr">
         <is>
@@ -7293,11 +7563,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J81" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="54" t="n">
-        <v>0</v>
+      <c r="J81" s="40" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K81" s="41" t="n">
+        <v>-0.05859756494563939</v>
       </c>
     </row>
     <row r="82">
@@ -7308,21 +7578,17 @@
       </c>
       <c r="B82" s="51" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C82" s="52" t="n">
-        <v>44000</v>
-      </c>
-      <c r="D82" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E82" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>205400</v>
+      </c>
+      <c r="D82" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="51" t="inlineStr">
         <is>
@@ -7344,83 +7610,83 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J82" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K82" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J82" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="55" t="inlineStr">
+      <c r="A83" s="51" t="inlineStr">
         <is>
           <t>Xavier Bertrand</t>
         </is>
       </c>
-      <c r="B83" s="55" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C83" s="56" t="n">
-        <v>335130</v>
-      </c>
-      <c r="D83" s="59" t="n">
-        <v>-270</v>
-      </c>
-      <c r="E83" s="60" t="n">
-        <v>-0.0805008944543828</v>
-      </c>
-      <c r="F83" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G83" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H83" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I83" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J83" s="57" t="n">
-        <v>12</v>
-      </c>
-      <c r="K83" s="58" t="n">
-        <v>0.003580828245564049</v>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C83" s="52" t="n">
+        <v>99000</v>
+      </c>
+      <c r="D83" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G83" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H83" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I83" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J83" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="51" t="inlineStr">
         <is>
-          <t>Édouard Philippe</t>
+          <t>Xavier Bertrand</t>
         </is>
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="C84" s="52" t="n">
-        <v>218132</v>
-      </c>
-      <c r="D84" s="32" t="n">
-        <v>132</v>
-      </c>
-      <c r="E84" s="34" t="n">
-        <v>0.0605504587156025</v>
+        <v>44000</v>
+      </c>
+      <c r="D84" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E84" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="F84" s="51" t="inlineStr">
         <is>
@@ -7442,58 +7708,62 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J84" s="32" t="n">
-        <v>281</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>0.1289872435747297</v>
+      <c r="J84" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K84" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="51" t="inlineStr">
-        <is>
-          <t>Édouard Philippe</t>
-        </is>
-      </c>
-      <c r="B85" s="51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C85" s="52" t="n">
-        <v>941200</v>
-      </c>
-      <c r="D85" s="40" t="n">
-        <v>-100</v>
-      </c>
-      <c r="E85" s="41" t="n">
-        <v>-0.01062360565176057</v>
-      </c>
-      <c r="F85" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G85" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H85" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I85" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J85" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="54" t="n">
-        <v>0</v>
+      <c r="A85" s="55" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="B85" s="55" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C85" s="56" t="n">
+        <v>335100</v>
+      </c>
+      <c r="D85" s="59" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E85" s="60" t="n">
+        <v>-0.008951750067143216</v>
+      </c>
+      <c r="F85" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G85" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H85" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I85" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J85" s="59" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K85" s="60" t="n">
+        <v>-0.005371242368357176</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -7504,17 +7774,17 @@
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C86" s="52" t="n">
-        <v>266000</v>
-      </c>
-      <c r="D86" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="54" t="n">
-        <v>0</v>
+        <v>218225</v>
+      </c>
+      <c r="D86" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="E86" s="34" t="n">
+        <v>0.04263473493113512</v>
       </c>
       <c r="F86" s="51" t="inlineStr">
         <is>
@@ -7536,11 +7806,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J86" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="54" t="n">
-        <v>0</v>
+      <c r="J86" s="32" t="n">
+        <v>374</v>
+      </c>
+      <c r="K86" s="34" t="n">
+        <v>0.1716769718752786</v>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
@@ -7551,470 +7821,506 @@
       </c>
       <c r="B87" s="51" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C87" s="52" t="n">
+        <v>941200</v>
+      </c>
+      <c r="D87" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I87" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J87" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C88" s="52" t="n">
+        <v>266000</v>
+      </c>
+      <c r="D88" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G88" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H88" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I88" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J88" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C87" s="52" t="n">
+      <c r="C89" s="52" t="n">
         <v>431000</v>
       </c>
-      <c r="D87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J87" s="32" t="n">
+      <c r="D89" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J89" s="32" t="n">
         <v>1000</v>
       </c>
-      <c r="K87" s="34" t="n">
+      <c r="K89" s="34" t="n">
         <v>0.2325581395348886</v>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="55" t="inlineStr">
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="55" t="inlineStr">
         <is>
           <t>Édouard Philippe</t>
         </is>
       </c>
-      <c r="B88" s="55" t="inlineStr">
+      <c r="B90" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C88" s="56" t="n">
-        <v>1856332</v>
-      </c>
-      <c r="D88" s="57" t="n">
-        <v>32</v>
-      </c>
-      <c r="E88" s="58" t="n">
-        <v>0.002245141373746762</v>
-      </c>
-      <c r="F88" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G88" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H88" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I88" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J88" s="57" t="n">
-        <v>1281</v>
-      </c>
-      <c r="K88" s="58" t="n">
-        <v>0.06905470523452806</v>
-      </c>
-    </row>
-    <row r="89" ht="30" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1"/>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="27" t="inlineStr">
+      <c r="C90" s="56" t="n">
+        <v>1856425</v>
+      </c>
+      <c r="D90" s="57" t="n">
+        <v>93</v>
+      </c>
+      <c r="E90" s="58" t="n">
+        <v>0.005009879698247843</v>
+      </c>
+      <c r="F90" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G90" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H90" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I90" s="55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J90" s="57" t="n">
+        <v>1374</v>
+      </c>
+      <c r="K90" s="58" t="n">
+        <v>0.07406804449041626</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1"/>
+    <row r="92" ht="30" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>CLASSEMENT CROISSANCE 7 JOURS</t>
         </is>
       </c>
-      <c r="B91" s="28" t="n"/>
-      <c r="C91" s="28" t="n"/>
-      <c r="D91" s="28" t="n"/>
-      <c r="E91" s="28" t="n"/>
-      <c r="F91" s="28" t="n"/>
-      <c r="G91" s="28" t="n"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="29" t="inlineStr">
+      <c r="B93" s="28" t="n"/>
+      <c r="C93" s="28" t="n"/>
+      <c r="D93" s="28" t="n"/>
+      <c r="E93" s="28" t="n"/>
+      <c r="F93" s="28" t="n"/>
+      <c r="G93" s="28" t="n"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B92" s="29" t="inlineStr">
+      <c r="B94" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
+      <c r="C94" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D92" s="29" t="inlineStr">
+      <c r="D94" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E92" s="29" t="inlineStr"/>
-      <c r="F92" s="29" t="inlineStr">
+      <c r="E94" s="29" t="inlineStr"/>
+      <c r="F94" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G92" s="29" t="inlineStr">
+      <c r="G94" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H92" s="29" t="inlineStr">
+      <c r="H94" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="13" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
         <is>
           <t>Pas encore assez d'historique pour cette periode.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1"/>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="27" t="inlineStr">
+    <row r="96" ht="30" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
         <is>
           <t>CLASSEMENT CROISSANCE 30 JOURS</t>
         </is>
       </c>
-      <c r="B95" s="28" t="n"/>
-      <c r="C95" s="28" t="n"/>
-      <c r="D95" s="28" t="n"/>
-      <c r="E95" s="28" t="n"/>
-      <c r="F95" s="28" t="n"/>
-      <c r="G95" s="28" t="n"/>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="29" t="inlineStr">
+      <c r="B97" s="28" t="n"/>
+      <c r="C97" s="28" t="n"/>
+      <c r="D97" s="28" t="n"/>
+      <c r="E97" s="28" t="n"/>
+      <c r="F97" s="28" t="n"/>
+      <c r="G97" s="28" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B96" s="29" t="inlineStr">
+      <c r="B98" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C96" s="29" t="inlineStr">
+      <c r="C98" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D96" s="29" t="inlineStr">
+      <c r="D98" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E96" s="29" t="inlineStr"/>
-      <c r="F96" s="29" t="inlineStr">
+      <c r="E98" s="29" t="inlineStr"/>
+      <c r="F98" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G96" s="29" t="inlineStr">
+      <c r="G98" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H96" s="29" t="inlineStr">
+      <c r="H98" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="13" t="inlineStr">
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>Pas encore assez d'historique pour cette periode.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="20" customHeight="1"/>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="27" t="inlineStr">
+    <row r="100" ht="30" customHeight="1"/>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
         <is>
           <t>CLASSEMENT CROISSANCE DEPUIS LE DEBUT DU SUIVI</t>
         </is>
       </c>
-      <c r="B99" s="28" t="n"/>
-      <c r="C99" s="28" t="n"/>
-      <c r="D99" s="28" t="n"/>
-      <c r="E99" s="28" t="n"/>
-      <c r="F99" s="28" t="n"/>
-      <c r="G99" s="28" t="n"/>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="29" t="inlineStr">
+      <c r="B101" s="28" t="n"/>
+      <c r="C101" s="28" t="n"/>
+      <c r="D101" s="28" t="n"/>
+      <c r="E101" s="28" t="n"/>
+      <c r="F101" s="28" t="n"/>
+      <c r="G101" s="28" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B100" s="29" t="inlineStr">
+      <c r="B102" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C100" s="29" t="inlineStr">
+      <c r="C102" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D100" s="29" t="inlineStr">
+      <c r="D102" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E100" s="29" t="inlineStr"/>
-      <c r="F100" s="29" t="inlineStr">
+      <c r="E102" s="29" t="inlineStr"/>
+      <c r="F102" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G100" s="29" t="inlineStr">
+      <c r="G102" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H100" s="29" t="inlineStr">
+      <c r="H102" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
-      </c>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="B101" s="45" t="inlineStr">
-        <is>
-          <t>David Lisnard</t>
-        </is>
-      </c>
-      <c r="C101" s="34" t="n">
-        <v>1.341517755649524</v>
-      </c>
-      <c r="D101" s="32" t="n">
-        <v>7376</v>
-      </c>
-      <c r="F101" s="45" t="inlineStr">
-        <is>
-          <t>Jean-Luc Mélenchon</t>
-        </is>
-      </c>
-      <c r="G101" s="32" t="n">
-        <v>9595</v>
-      </c>
-      <c r="H101" s="34" t="n">
-        <v>0.1797442218180345</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B102" s="45" t="inlineStr">
-        <is>
-          <t>Gabriel Attal</t>
-        </is>
-      </c>
-      <c r="C102" s="34" t="n">
-        <v>0.4870280901185797</v>
-      </c>
-      <c r="D102" s="32" t="n">
-        <v>4502</v>
-      </c>
-      <c r="F102" s="45" t="inlineStr">
-        <is>
-          <t>David Lisnard</t>
-        </is>
-      </c>
-      <c r="G102" s="32" t="n">
-        <v>7376</v>
-      </c>
-      <c r="H102" s="34" t="n">
-        <v>1.341517755649524</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C103" s="34" t="n">
+        <v>1.523211931068968</v>
+      </c>
+      <c r="D103" s="32" t="n">
+        <v>8375</v>
+      </c>
+      <c r="F103" s="45" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="G103" s="32" t="n">
+        <v>8859</v>
+      </c>
+      <c r="H103" s="34" t="n">
+        <v>0.165956650451915</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C104" s="34" t="n">
+        <v>0.3150103940676496</v>
+      </c>
+      <c r="D104" s="32" t="n">
+        <v>4446</v>
+      </c>
+      <c r="F104" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="G104" s="32" t="n">
+        <v>8375</v>
+      </c>
+      <c r="H104" s="34" t="n">
+        <v>1.523211931068968</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="B103" s="45" t="inlineStr">
-        <is>
-          <t>Jean-Luc Mélenchon</t>
-        </is>
-      </c>
-      <c r="C103" s="34" t="n">
-        <v>0.1797442218180345</v>
-      </c>
-      <c r="D103" s="32" t="n">
-        <v>9595</v>
-      </c>
-      <c r="F103" s="45" t="inlineStr">
+      <c r="B105" s="45" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C105" s="34" t="n">
+        <v>0.1700454386578176</v>
+      </c>
+      <c r="D105" s="32" t="n">
+        <v>973</v>
+      </c>
+      <c r="F105" s="45" t="inlineStr">
         <is>
           <t>Gabriel Attal</t>
         </is>
       </c>
-      <c r="G103" s="32" t="n">
-        <v>4502</v>
-      </c>
-      <c r="H103" s="34" t="n">
-        <v>0.4870280901185797</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="B104" s="63" t="inlineStr">
-        <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
-      <c r="C104" s="34" t="n">
-        <v>0.1536176162181047</v>
-      </c>
-      <c r="D104" s="32" t="n">
-        <v>879</v>
-      </c>
-      <c r="F104" s="63" t="inlineStr">
-        <is>
-          <t>Édouard Philippe</t>
-        </is>
-      </c>
-      <c r="G104" s="32" t="n">
-        <v>1281</v>
-      </c>
-      <c r="H104" s="34" t="n">
-        <v>0.06905470523452806</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="62" t="n">
-        <v>5</v>
-      </c>
-      <c r="B105" s="63" t="inlineStr">
-        <is>
-          <t>Édouard Philippe</t>
-        </is>
-      </c>
-      <c r="C105" s="34" t="n">
-        <v>0.06905470523452806</v>
-      </c>
-      <c r="D105" s="32" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F105" s="63" t="inlineStr">
-        <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
       <c r="G105" s="32" t="n">
-        <v>879</v>
+        <v>4446</v>
       </c>
       <c r="H105" s="34" t="n">
-        <v>0.1536176162181047</v>
+        <v>0.3150103940676496</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B106" s="63" t="inlineStr">
         <is>
-          <t>Bruno Retailleau</t>
+          <t>Jean-Luc Mélenchon</t>
         </is>
       </c>
       <c r="C106" s="34" t="n">
-        <v>0.05174182204477074</v>
+        <v>0.165956650451915</v>
       </c>
       <c r="D106" s="32" t="n">
-        <v>226</v>
+        <v>8859</v>
       </c>
       <c r="F106" s="63" t="inlineStr">
         <is>
-          <t>Marine Le Pen</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="G106" s="32" t="n">
-        <v>317</v>
+        <v>1374</v>
       </c>
       <c r="H106" s="34" t="n">
-        <v>0.005412524889925052</v>
+        <v>0.07406804449041626</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B107" s="63" t="inlineStr">
         <is>
-          <t>Raphaël Glucksmann</t>
+          <t>Bruno Retailleau</t>
         </is>
       </c>
       <c r="C107" s="34" t="n">
-        <v>0.02356774793714767</v>
+        <v>0.1020198345538903</v>
       </c>
       <c r="D107" s="32" t="n">
-        <v>265</v>
+        <v>516</v>
       </c>
       <c r="F107" s="63" t="inlineStr">
         <is>
-          <t>Raphaël Glucksmann</t>
+          <t>Marine Tondelier</t>
         </is>
       </c>
       <c r="G107" s="32" t="n">
-        <v>265</v>
+        <v>973</v>
       </c>
       <c r="H107" s="34" t="n">
-        <v>0.02356774793714767</v>
+        <v>0.1700454386578176</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B108" s="63" t="inlineStr">
         <is>
-          <t>Marine Le Pen</t>
+          <t>Édouard Philippe</t>
         </is>
       </c>
       <c r="C108" s="34" t="n">
-        <v>0.005412524889925052</v>
+        <v>0.07406804449041626</v>
       </c>
       <c r="D108" s="32" t="n">
-        <v>317</v>
+        <v>1374</v>
       </c>
       <c r="F108" s="63" t="inlineStr">
         <is>
@@ -8022,64 +8328,118 @@
         </is>
       </c>
       <c r="G108" s="32" t="n">
-        <v>226</v>
+        <v>516</v>
       </c>
       <c r="H108" s="34" t="n">
-        <v>0.05174182204477074</v>
+        <v>0.1020198345538903</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B109" s="63" t="inlineStr">
         <is>
-          <t>Xavier Bertrand</t>
+          <t>Raphaël Glucksmann</t>
         </is>
       </c>
       <c r="C109" s="34" t="n">
-        <v>0.003580828245564049</v>
+        <v>0.03397313098865151</v>
       </c>
       <c r="D109" s="32" t="n">
-        <v>12</v>
+        <v>382</v>
       </c>
       <c r="F109" s="63" t="inlineStr">
         <is>
-          <t>Xavier Bertrand</t>
+          <t>Marine Le Pen</t>
         </is>
       </c>
       <c r="G109" s="32" t="n">
-        <v>12</v>
+        <v>472</v>
       </c>
       <c r="H109" s="34" t="n">
-        <v>0.003580828245564049</v>
+        <v>0.008059027596374335</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B110" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C110" s="34" t="n">
+        <v>0.008059027596374335</v>
+      </c>
+      <c r="D110" s="32" t="n">
+        <v>472</v>
+      </c>
+      <c r="F110" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="G110" s="32" t="n">
+        <v>382</v>
+      </c>
+      <c r="H110" s="34" t="n">
+        <v>0.03397313098865151</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B111" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C111" s="34" t="n">
+        <v>0.005203708137635488</v>
+      </c>
+      <c r="D111" s="32" t="n">
+        <v>168</v>
+      </c>
+      <c r="F111" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="G111" s="32" t="n">
+        <v>168</v>
+      </c>
+      <c r="H111" s="34" t="n">
+        <v>0.005203708137635488</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="B110" s="63" t="inlineStr">
-        <is>
-          <t>Jordan Bardella</t>
-        </is>
-      </c>
-      <c r="C110" s="41" t="n">
-        <v>-3.097445320232595e-05</v>
-      </c>
-      <c r="D110" s="40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F110" s="63" t="inlineStr">
-        <is>
-          <t>Jordan Bardella</t>
-        </is>
-      </c>
-      <c r="G110" s="40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H110" s="41" t="n">
-        <v>-3.097445320232595e-05</v>
+      <c r="B112" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C112" s="41" t="n">
+        <v>-0.005371242368357176</v>
+      </c>
+      <c r="D112" s="40" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F112" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="G112" s="40" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H112" s="41" t="n">
+        <v>-0.005371242368357176</v>
       </c>
     </row>
   </sheetData>
@@ -8139,7 +8499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG6"/>
+  <dimension ref="A1:BG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8453,13 +8813,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>436784</v>
+        <v>505784</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>549825</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>924382</v>
+        <v>1411382</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>5338141</v>
@@ -8600,13 +8960,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>437200</v>
+        <v>506200</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>546800</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>925380</v>
+        <v>1412380</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>5340366</v>
@@ -8635,13 +8995,13 @@
         </is>
       </c>
       <c r="N4" s="14" t="n">
-        <v>1000.95</v>
+        <v>1000.82</v>
       </c>
       <c r="O4" s="14" t="n">
         <v>994.5</v>
       </c>
       <c r="P4" s="14" t="n">
-        <v>1001.08</v>
+        <v>1000.71</v>
       </c>
       <c r="Q4" s="14" t="n">
         <v>1000.42</v>
@@ -8746,12 +9106,6 @@
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>437300</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>926700</v>
-      </c>
       <c r="G5" s="2" t="n">
         <v>5857000</v>
       </c>
@@ -8763,12 +9117,6 @@
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="N5" s="14" t="n">
-        <v>1001.18</v>
-      </c>
-      <c r="P5" s="14" t="n">
-        <v>1002.51</v>
-      </c>
       <c r="S5" s="14" t="n">
         <v>1000.04</v>
       </c>
@@ -8878,15 +9226,9 @@
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>437010</v>
-      </c>
       <c r="C6" s="2" t="n">
         <v>557201</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>928884</v>
-      </c>
       <c r="E6" s="2" t="n">
         <v>5347736</v>
       </c>
@@ -8913,15 +9255,9 @@
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="N6" s="14" t="n">
-        <v>1000.52</v>
-      </c>
       <c r="O6" s="14" t="n">
         <v>1013.42</v>
       </c>
-      <c r="P6" s="14" t="n">
-        <v>1004.87</v>
-      </c>
       <c r="Q6" s="14" t="n">
         <v>1001.8</v>
       </c>
@@ -9038,6 +9374,174 @@
       </c>
       <c r="BD6" s="14" t="n">
         <v>1004.71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>506300</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>558200</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1415828</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5347000</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3228635</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>5857258</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>573173</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1124800</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>335100</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1856425</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>1001.02</v>
+      </c>
+      <c r="O7" s="14" t="n">
+        <v>1015.23</v>
+      </c>
+      <c r="P7" s="14" t="n">
+        <v>1003.15</v>
+      </c>
+      <c r="Q7" s="14" t="n">
+        <v>1001.66</v>
+      </c>
+      <c r="R7" s="14" t="n">
+        <v>1000.05</v>
+      </c>
+      <c r="S7" s="14" t="n">
+        <v>1000.08</v>
+      </c>
+      <c r="T7" s="14" t="n">
+        <v>1001.7</v>
+      </c>
+      <c r="U7" s="14" t="n">
+        <v>1000.34</v>
+      </c>
+      <c r="V7" s="14" t="n">
+        <v>999.95</v>
+      </c>
+      <c r="W7" s="14" t="n">
+        <v>1000.74</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="Z7" s="14" t="n">
+        <v>1003.94</v>
+      </c>
+      <c r="AA7" s="14" t="n">
+        <v>1035.35</v>
+      </c>
+      <c r="AB7" s="14" t="n">
+        <v>1000.75</v>
+      </c>
+      <c r="AC7" s="14" t="n">
+        <v>1010.57</v>
+      </c>
+      <c r="AD7" s="14" t="n">
+        <v>999.91</v>
+      </c>
+      <c r="AE7" s="14" t="n">
+        <v>1000.62</v>
+      </c>
+      <c r="AF7" s="14" t="n">
+        <v>1002.73</v>
+      </c>
+      <c r="AG7" s="14" t="n">
+        <v>1000.76</v>
+      </c>
+      <c r="AH7" s="14" t="n">
+        <v>999.41</v>
+      </c>
+      <c r="AI7" s="14" t="n">
+        <v>1001.72</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="AL7" s="14" t="n">
+        <v>1000.47</v>
+      </c>
+      <c r="AM7" s="14" t="n">
+        <v>1002.09</v>
+      </c>
+      <c r="AN7" s="14" t="n">
+        <v>1000.35</v>
+      </c>
+      <c r="AO7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" s="14" t="n">
+        <v>1000.48</v>
+      </c>
+      <c r="AQ7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS7" s="14" t="n">
+        <v>999.6799999999999</v>
+      </c>
+      <c r="AT7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="AX7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY7" s="14" t="n">
+        <v>1021.86</v>
+      </c>
+      <c r="AZ7" s="14" t="n">
+        <v>1000.59</v>
+      </c>
+      <c r="BA7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BB7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BD7" s="14" t="n">
+        <v>1005.88</v>
       </c>
     </row>
   </sheetData>
